--- a/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>COST</t>
   </si>
@@ -656,413 +656,439 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45340</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45256</v>
+      </c>
+      <c r="F7" s="2">
         <v>45172</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44969</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44885</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44801</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44689</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44605</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44521</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44437</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44325</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44241</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44157</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44073</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43961</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43877</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43793</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43709</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43597</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43513</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43429</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43345</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43233</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43149</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43065</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42981</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42862</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42778</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42694</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>58442000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>57799000</v>
+      </c>
+      <c r="F8" s="3">
         <v>78939000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>53648000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>55266000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>54437000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>72091000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>52596000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>51904000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>50363000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>62675000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>45277000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>44769000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>43208000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>53383000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>37266000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>39072000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>37040000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>47498000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>34740000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>35396000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>35069000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>44411000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>32361000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>32995000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>31809000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>42300000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>28860000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>29766000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>28099000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>36560000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>51140000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>50457000</v>
+      </c>
+      <c r="F9" s="3">
         <v>69219000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>47175000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>48423000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>47769000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>63558000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>46355000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>45517000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>43952000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>54733000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>39415000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>39078000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>37458000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>46337000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>32205000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>34056000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>32233000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>41310000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>30233000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>30720000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>30623000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>38671000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>28131000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>28733000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>27617000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>36697000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>24970000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>25927000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>24288000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>31649000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7302000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7342000</v>
+      </c>
+      <c r="F10" s="3">
         <v>9720000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>6473000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>6843000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>6668000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>8533000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>6241000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>6387000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>6411000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>7942000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5862000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>5691000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>5750000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>7046000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>5061000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>5016000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>4807000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>6188000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>4507000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>4676000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>4446000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>5740000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>4230000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>4262000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>4192000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>5603000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3890000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3839000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>3811000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>4911000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1095,8 +1121,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1187,8 +1215,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1279,8 +1313,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1296,41 +1336,41 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>118000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>84000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>57000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>246000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>212000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>370000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>302000</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1344,11 +1384,11 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1371,31 +1411,37 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
@@ -1412,23 +1458,23 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3">
         <v>16000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>7000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>4000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>4000</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>8</v>
@@ -1442,11 +1488,11 @@
       <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1463,8 +1509,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1494,192 +1546,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>56380000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>55815000</v>
+      </c>
+      <c r="F17" s="3">
         <v>76158000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>51969000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>53363000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>52686000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>69594000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>50805000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>50092000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>48670000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>60400000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>43614000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>43429000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>41778000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>51454000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>36087000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>37806000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>35979000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>46035000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>33618000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>34193000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>34120000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>42965000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>31294000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>31979000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>30858000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>40850000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>27892000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>28922000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>27250000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>35369000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2062000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1984000</v>
+      </c>
+      <c r="F18" s="3">
         <v>2781000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1679000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1903000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1751000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2497000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1791000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1812000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1693000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2275000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1663000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1340000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1430000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1929000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1179000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1266000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1061000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1463000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1122000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1203000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>949000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1446000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1067000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1016000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>951000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1450000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>968000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>844000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>849000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1191000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1712,468 +1778,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>216000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>160000</v>
+      </c>
+      <c r="F20" s="3">
         <v>238000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>128000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>114000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>53000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>67000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>71000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>25000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>42000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>68000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>27000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>19000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>29000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>21000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>45000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>35000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>74000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>36000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>46000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>22000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>51000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>41000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>7000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>22000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>22000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>18000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>26000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2792000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2645000</v>
+      </c>
+      <c r="F21" s="3">
         <v>3707000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2279000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2487000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2251000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3158000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2300000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2273000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2167000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2902000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2092000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1775000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1863000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2425000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1582000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1700000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1465000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2010000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1494000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1601000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1302000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1928000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1435000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1367000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1308000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1913000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1152000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1172000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1628000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>38000</v>
+      </c>
+      <c r="F22" s="3">
         <v>56000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>36000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>34000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>34000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>48000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>35000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>36000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>39000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>52000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>40000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>40000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>39000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>51000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>37000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>34000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>38000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>45000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>35000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>34000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>36000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>48000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>37000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>37000</v>
       </c>
       <c r="AA22" s="3">
         <v>37000</v>
       </c>
       <c r="AB22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>53000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>21000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>31000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>29000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2237000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="F23" s="3">
         <v>2963000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1771000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1983000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1770000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2516000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1827000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1801000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1696000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2291000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1650000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1319000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1420000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1869000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1163000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1277000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1058000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1492000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1123000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1215000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>935000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1449000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1071000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>986000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>936000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1419000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>965000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>809000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>846000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>1181000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>494000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>517000</v>
+      </c>
+      <c r="F24" s="3">
         <v>803000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>469000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>517000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>406000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>638000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>455000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>481000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>351000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>597000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>417000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>348000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>239000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>465000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>311000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>330000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>202000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>340000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>280000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>377000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>185000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>402000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>310000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>247000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>285000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>487000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>259000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>288000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>291000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>396000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2264,192 +2362,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1743000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1589000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2160000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1302000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1466000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1364000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1878000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1372000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1320000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1345000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1694000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1233000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>971000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1181000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1404000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>852000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>947000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>856000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1152000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>843000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>838000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>750000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1047000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>761000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>739000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>651000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>932000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>706000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>521000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>555000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>785000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1743000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1589000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2160000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1302000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1466000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1364000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1868000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1353000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1299000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1324000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1670000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1220000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>951000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1166000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1389000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>838000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>931000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>844000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1139000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>833000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>826000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>740000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1037000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>749000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>727000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>640000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>919000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>700000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>515000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>545000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2540,8 +2656,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,53 +2694,53 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>-42000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>73000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>63000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>27000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>6000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>1000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-26000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2632,8 +2754,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2724,8 +2852,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2816,192 +2950,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-216000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-238000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-128000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-114000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-53000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-67000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-71000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-25000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-42000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-68000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-27000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-19000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-29000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>9000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-21000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-45000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-35000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-74000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-36000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-46000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-22000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-51000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>4000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1743000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1589000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2160000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1302000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1466000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1364000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1868000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1353000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1299000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1324000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1670000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1220000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>951000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1166000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1389000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>838000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>931000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>844000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1097000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>906000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>889000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>767000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1043000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>750000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>701000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>640000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>919000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>700000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>515000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>545000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3092,197 +3244,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1743000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1589000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2160000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1302000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1466000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1364000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1868000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1353000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1299000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1324000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1670000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1220000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>951000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1166000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1389000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>838000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>931000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>844000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1097000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>906000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>889000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>767000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1043000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>750000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>701000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>640000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>919000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>700000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>515000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>545000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45340</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45256</v>
+      </c>
+      <c r="F38" s="2">
         <v>45172</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44969</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44885</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44801</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44689</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44605</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44521</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44437</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44325</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44241</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44157</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44073</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43961</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43877</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43793</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43709</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43597</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43513</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43429</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43345</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43233</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43149</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43065</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42981</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42862</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42778</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42694</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3315,8 +3485,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3349,560 +3521,598 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9095000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>17011000</v>
+      </c>
+      <c r="F41" s="3">
         <v>13700000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>12493000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12970000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>10856000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10203000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>11193000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>11819000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>12751000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>11258000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10226000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>8637000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>13590000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>12277000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>10826000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>7786000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>9027000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>8384000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>7013000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>6080000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>6778000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>6055000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>5877000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>4781000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>5689000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>4546000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>4538000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>4744000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>4805000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3379000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>853000</v>
+      </c>
+      <c r="F42" s="3">
         <v>1534000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1215000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>735000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>817000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>846000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>638000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>477000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>725000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>917000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>900000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>617000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>833000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1028000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>948000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>929000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>993000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1060000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>1154000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>1042000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1175000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1204000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1167000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1049000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1196000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1233000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1187000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1221000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1311000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>1350000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2542000</v>
+      </c>
+      <c r="F43" s="3">
         <v>2285000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2502000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2714000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2312000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2241000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1991000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2232000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1932000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1803000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1595000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1934000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1646000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1550000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1507000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1988000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1711000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1535000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1704000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1995000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1795000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1669000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1593000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2001000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1559000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1432000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1462000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1597000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>1498000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1252000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17075000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>18001000</v>
+      </c>
+      <c r="F44" s="3">
         <v>16651000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>16324000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>16081000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>18571000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>17907000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>17623000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>16485000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>16942000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>14215000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>13975000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>13865000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>14901000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>12242000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>11010000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>11850000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>13818000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>11395000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>11304000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>11356000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>12205000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>11040000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>10626000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>10671000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>11213000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>9834000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>9736000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>9530000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>10721000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>8969000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1971000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1673000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1709000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1755000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1830000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1594000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1499000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1563000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1552000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1500000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1312000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1220000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1255000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1126000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1023000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>963000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1150000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1094000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1111000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1110000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1175000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1001000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>321000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>430000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>397000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>240000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>272000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>333000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>368000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>235000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>268000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32146000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>40080000</v>
+      </c>
+      <c r="F46" s="3">
         <v>35879000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>34289000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>34330000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>34150000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>32696000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>33008000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>32565000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>33850000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>29505000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>27916000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>26308000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>32096000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>28120000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>25254000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>23703000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>26643000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>23485000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>22285000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>21648000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>22954000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>20289000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>19693000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>18899000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>19897000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>17317000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>17256000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>17460000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>18570000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>15218000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3993,111 +4203,123 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30341000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>29840000</v>
+      </c>
+      <c r="F48" s="3">
         <v>29397000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>28737000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>28583000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>27931000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>27420000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>26874000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>26892000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>26790000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>26382000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>26052000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>25418000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>25073000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>25187000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>24276000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>24077000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>23834000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>20890000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>20475000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>20145000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>19879000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>19681000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>19178000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>19049000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>18682000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>18161000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>17535000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>17342000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>17156000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>17043000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>994000</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>8</v>
+      <c r="F49" s="3">
+        <v>994000</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>8</v>
@@ -4114,29 +4336,29 @@
       <c r="K49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="3">
+      <c r="L49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N49" s="3">
         <v>1290000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1234000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1235000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1217000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1271000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1242000</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
@@ -4150,11 +4372,11 @@
       <c r="W49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -4177,8 +4399,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4269,8 +4497,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4361,100 +4595,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3836000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3803000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2724000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3726000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3935000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3946000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>4050000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3970000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3621000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3509000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2091000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2072000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1957000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1831000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>978000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>960000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1002000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>954000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1025000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>992000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1006000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>981000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>860000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>734000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>755000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>799000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>869000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>840000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>828000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>806000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>902000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4545,100 +4791,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>66323000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>73723000</v>
+      </c>
+      <c r="F54" s="3">
         <v>68994000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>66752000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>66848000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>66027000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>64166000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>63852000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>63078000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>64149000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>59268000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>57274000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>54918000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>60217000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>55556000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>51732000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>48782000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>51431000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>45400000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>43752000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>42799000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>43814000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>40830000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>39605000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>38703000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>39378000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>36347000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>35631000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>35630000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>36532000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>33163000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4671,8 +4929,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4705,560 +4965,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17494000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>20357000</v>
+      </c>
+      <c r="F57" s="3">
         <v>17483000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>16853000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>16407000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>18348000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>17848000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>17651000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>17089000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>19561000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>16278000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>15538000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>14383000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>17014000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>14172000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>10813000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>11072000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>14440000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>11679000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>11331000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>10711000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>13133000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>11237000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>10705000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>10061000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>11992000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>9608000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>9425000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>8764000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>11003000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>7612000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1080000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1080000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1081000</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>76000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>71000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>73000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>77000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>799000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>799000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>92000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>95000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>96000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>126000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1526000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>518000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1712000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1699000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1699000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1698000</v>
       </c>
-      <c r="W58" s="3" t="s">
+      <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>90000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>119000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>122000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>116000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>86000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1158000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>2257000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1159000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1100000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16114000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>15331000</v>
+      </c>
+      <c r="F59" s="3">
         <v>15019000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>14855000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>16033000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>14648000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>14077000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>14117000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>14456000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>12982000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>12364000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>12352000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>12086000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>15557000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>10546000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>10440000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>11105000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>10113000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>9859000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>9802000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>10041000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>9340000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>8599000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>8587000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>8730000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>8252000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>7801000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>10811000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>7839000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>6999000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>6863000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34688000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>36768000</v>
+      </c>
+      <c r="F60" s="3">
         <v>33583000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>31708000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>32516000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>33067000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>31998000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>31845000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>31545000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>33342000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>29441000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>27982000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>26564000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>32667000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>24844000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>22779000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>22695000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>26265000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>23237000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>22832000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>22450000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>22473000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>19926000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>19411000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>18913000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>20360000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>17495000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>21394000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>18860000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>19161000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>15575000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5865000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5866000</v>
+      </c>
+      <c r="F61" s="3">
         <v>5377000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6497000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6506000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6472000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6484000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6507000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6658000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6667000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6692000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7495000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7522000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>7529000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8171000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8227000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>5643000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>5495000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>5124000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>4799000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>4794000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>6480000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>6487000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>6492000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>6505000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>6478000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>6573000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2821000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2815000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>3933000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>4061000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5010000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4942000</v>
+      </c>
+      <c r="F62" s="3">
         <v>4976000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4974000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5027000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>5012000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>5037000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4987000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4899000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5140000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5057000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4823000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4703000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>4712000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3836000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3523000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3445000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3447000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1455000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1301000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1372000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1382000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1314000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1255000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1232000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1184000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1200000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1231000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1243000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1207000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1195000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5349,8 +5647,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5441,8 +5745,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5533,100 +5843,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45563000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>47576000</v>
+      </c>
+      <c r="F66" s="3">
         <v>43936000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>43184000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>44054000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>44556000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>43524000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>43884000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>43660000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>45686000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>41704000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>40792000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>39266000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>45357000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>37272000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>34930000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>32168000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>35570000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>30157000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>29266000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>28941000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>30647000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>28031000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>27462000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>26949000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>28300000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>25569000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>25733000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>23190000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>24559000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>21084000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5659,8 +5981,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5751,8 +6075,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5843,8 +6173,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5935,8 +6271,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6027,100 +6369,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14980000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>20499000</v>
+      </c>
+      <c r="F72" s="3">
         <v>19521000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>18035000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>17341000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>16412000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>15585000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>14294000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>13474000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>12606000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>11666000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>10466000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>9766000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>9232000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>12879000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>11883000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>11384000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>10787000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>10258000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>9496000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>8916000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>8387000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>7887000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>7176000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>6727000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>6300000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>5988000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>5508000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>8140000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>7882000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>7686000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6211,8 +6565,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6303,8 +6663,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6395,100 +6761,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20760000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>26147000</v>
+      </c>
+      <c r="F76" s="3">
         <v>25058000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>23568000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>22794000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>21471000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20642000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>19968000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>19418000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>18463000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>17564000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>16482000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15652000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>14860000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>18284000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>16802000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>16614000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>15861000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>15243000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14486000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>13858000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>13167000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>12799000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>12143000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>11754000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>11078000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>10778000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>9898000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>12440000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>11973000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>12079000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6579,197 +6957,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45340</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45256</v>
+      </c>
+      <c r="F80" s="2">
         <v>45172</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44969</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44885</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44801</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44689</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44605</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44521</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44437</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44325</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44241</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44157</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44073</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43961</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43877</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43793</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43709</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43597</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43513</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43429</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43345</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43233</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43149</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43065</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42981</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42862</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42778</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42694</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1743000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1589000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2160000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1302000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1466000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1364000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1868000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1353000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1299000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1324000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1670000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1220000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>951000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1166000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1389000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>838000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>931000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>844000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1097000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>906000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>889000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>767000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1043000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>750000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>701000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>640000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>919000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>700000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>515000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>545000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6802,100 +7198,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>514000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>501000</v>
+      </c>
+      <c r="F83" s="3">
         <v>688000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>472000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>470000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>447000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>594000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>438000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>436000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>432000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>559000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>402000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>416000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>404000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>505000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>382000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>389000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>369000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>473000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>336000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>352000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>331000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>431000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>327000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>344000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>335000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>441000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>320000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>312000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>297000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6986,8 +7390,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7078,8 +7488,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7170,8 +7586,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7262,8 +7684,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7354,100 +7782,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>731000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4651000</v>
+      </c>
+      <c r="F89" s="3">
         <v>3725000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1541000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>3192000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2610000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2506000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1227000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>401000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3258000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2940000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3333000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>38000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2647000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4242000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1898000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>619000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2102000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2293000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2105000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-219000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2177000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1554000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2105000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>109000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>2006000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1834000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1606000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>493000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2793000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-169000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7480,100 +7920,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1031000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1040000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1556000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-820000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-890000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1057000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1259000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-854000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-723000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1055000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1094000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1028000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-573000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-893000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-852000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-698000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-545000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-715000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-672000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-587000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-730000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1056000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-585000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-508000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-820000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-779000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-540000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-516000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-667000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-849000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7664,8 +8112,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7756,100 +8210,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1386000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-366000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-808000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1057000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1487000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-481000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-912000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1155000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1343000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-355000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-682000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-941000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1850000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-470000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-630000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-920000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-774000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-434000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-737000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1095000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-694000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-785000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-816000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-498000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-397000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-655000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1025000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7882,100 +8348,108 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-7107000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-905000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-452000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-399000</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-400000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-797000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-351000</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-350000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-698000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-310000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-4430000</v>
       </c>
       <c r="O96" s="3">
         <v>-310000</v>
       </c>
       <c r="P96" s="3">
+        <v>-4430000</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>-310000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-619000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-287000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-573000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-286000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-251000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-501000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-250000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-219000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-220000</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-3508000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-198000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>0</v>
       </c>
       <c r="AE96" s="3">
         <v>-198000</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>-198000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-394000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8066,8 +8540,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8158,8 +8638,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8250,280 +8736,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7276000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-974000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-664000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-735000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-352000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-863000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1940000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-676000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-828000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-839000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-719000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-419000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-4650000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-700000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1918000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>2999000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1392000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-836000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-397000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-49000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-700000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-267000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-266000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-690000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-165000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-660000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-331000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-29000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>82000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-37000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-69000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-142000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-24000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-34000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>18000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>14000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>48000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>68000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>7000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-17000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-49000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>46000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>67000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>8000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-52000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7916000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3311000</v>
+      </c>
+      <c r="F102" s="3">
         <v>1207000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-477000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2114000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>653000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-990000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-626000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-932000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1493000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1032000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1589000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-4953000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1313000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1451000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3040000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1241000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>643000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1371000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>933000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-698000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>723000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>178000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>1096000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-908000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1143000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>8000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-206000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1426000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-1505000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>COST</t>
   </si>
@@ -656,439 +656,452 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45424</v>
+      </c>
+      <c r="E7" s="2">
         <v>45340</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45256</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45172</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45053</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44969</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44885</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44801</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44689</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44605</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44521</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44437</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44325</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44241</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44157</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44073</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43961</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43877</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43793</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43709</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43597</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43513</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43429</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43345</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43233</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43149</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43065</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42981</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42862</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42778</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42694</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>58515000</v>
+      </c>
+      <c r="E8" s="3">
         <v>58442000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>57799000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>78939000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>53648000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>55266000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>54437000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>72091000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>52596000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>51904000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>50363000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>62675000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>45277000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>44769000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>43208000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>53383000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>37266000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>39072000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37040000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>47498000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34740000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>35396000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>35069000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>44411000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>32361000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32995000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>31809000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>42300000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>28860000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>29766000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>28099000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>36560000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>51173000</v>
+      </c>
+      <c r="E9" s="3">
         <v>51140000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>50457000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>69219000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>47175000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>48423000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>47769000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>63558000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>46355000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>45517000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>43952000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>54733000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39415000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39078000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>37458000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>46337000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>32205000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>34056000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>32233000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>41310000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>30233000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>30720000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>30623000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>38671000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>28131000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>28733000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>27617000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>36697000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>24970000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>25927000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>24288000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>31649000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7342000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7302000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7342000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9720000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6473000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6843000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6668000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8533000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6241000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6387000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6411000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7942000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5862000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5691000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5750000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7046000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5061000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5016000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4807000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6188000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4507000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4676000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4446000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5740000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4230000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4262000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4192000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5603000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3890000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3839000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3811000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4911000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1123,8 +1136,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,8 +1235,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,8 +1336,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1342,8 +1362,8 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1352,28 +1372,28 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>118000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>84000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>57000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>246000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>212000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>370000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>302000</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1390,8 +1410,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1417,8 +1437,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1443,8 +1466,8 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>8</v>
@@ -1464,20 +1487,20 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3">
         <v>16000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>4000</v>
       </c>
       <c r="U15" s="3">
         <v>4000</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
+      <c r="V15" s="3">
+        <v>4000</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>8</v>
@@ -1494,8 +1517,8 @@
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1515,8 +1538,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1548,204 +1574,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>56318000</v>
+      </c>
+      <c r="E17" s="3">
         <v>56380000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>55815000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>76158000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>51969000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>53363000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>52686000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>69594000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>50805000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>50092000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>48670000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>60400000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>43614000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>43429000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>41778000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>51454000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>36087000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>37806000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>35979000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>46035000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>33618000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>34193000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>34120000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>42965000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>31294000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>31979000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>30858000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>40850000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>27892000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>28922000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>27250000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>35369000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2197000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2062000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1984000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2781000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1679000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1903000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1751000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2497000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1791000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1812000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1693000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2275000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1663000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1340000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1430000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1929000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1179000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1266000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1061000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1463000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1122000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1203000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>949000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1446000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1067000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1016000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>951000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1450000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>968000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>844000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>849000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1191000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,204 +1813,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E20" s="3">
         <v>216000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>160000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>238000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>128000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>114000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>53000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>67000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>71000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>25000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>42000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>68000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>27000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>19000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>29000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>21000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>45000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>35000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>74000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>36000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>46000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>22000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>51000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>41000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>22000</v>
       </c>
       <c r="AD20" s="3">
         <v>22000</v>
       </c>
       <c r="AE20" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AF20" s="3">
         <v>18000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>26000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2841000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2792000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2645000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3707000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2279000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2487000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2251000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3158000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2300000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2273000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2167000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2902000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2092000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1775000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1863000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2425000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1582000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1700000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1465000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2010000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1494000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1601000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1302000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1928000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1435000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1367000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1308000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1913000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1152000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1172000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1628000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1985,73 +2025,73 @@
         <v>41000</v>
       </c>
       <c r="E22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F22" s="3">
         <v>38000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>56000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>36000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>34000</v>
       </c>
       <c r="I22" s="3">
         <v>34000</v>
       </c>
       <c r="J22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="K22" s="3">
         <v>48000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>35000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>36000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>52000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>40000</v>
       </c>
       <c r="P22" s="3">
         <v>40000</v>
       </c>
       <c r="Q22" s="3">
+        <v>40000</v>
+      </c>
+      <c r="R22" s="3">
         <v>39000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>51000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>37000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>34000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>38000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>45000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>35000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>34000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>36000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>48000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>37000</v>
       </c>
       <c r="AB22" s="3">
         <v>37000</v>
@@ -2060,218 +2100,227 @@
         <v>37000</v>
       </c>
       <c r="AD22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>53000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>21000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>31000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>29000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2284000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2237000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2106000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2963000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1771000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1983000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1770000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2516000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1827000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1801000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1696000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2291000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1650000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1319000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1420000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1869000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1163000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1277000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1058000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1492000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1123000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1215000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>935000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1449000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1071000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>986000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>936000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1419000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>965000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>809000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>846000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1181000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>603000</v>
+      </c>
+      <c r="E24" s="3">
         <v>494000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>517000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>803000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>469000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>517000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>406000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>638000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>455000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>481000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>351000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>597000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>417000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>348000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>239000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>465000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>311000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>330000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>202000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>340000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>280000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>377000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>185000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>402000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>310000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>247000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>285000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>487000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>259000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>288000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>291000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>396000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2368,204 +2417,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1681000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1743000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1589000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2160000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1302000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1466000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1364000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1878000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1372000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1320000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1345000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1694000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1233000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>971000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1181000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1404000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>852000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>947000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>856000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1152000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>843000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>838000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>750000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>761000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>739000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>651000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>932000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>706000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>521000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>555000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>785000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1681000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1743000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1589000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2160000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1302000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1466000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1364000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1868000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1353000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1299000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1324000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1670000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1220000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>951000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1166000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1389000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>838000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>931000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>844000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1139000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>833000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>826000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>740000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1037000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>749000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>727000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>640000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>919000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>700000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>515000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>545000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2662,8 +2720,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2700,8 +2761,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2709,11 +2770,11 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
+      <c r="R29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2721,29 +2782,29 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>-42000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>73000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>63000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>27000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>6000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>1000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-26000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2760,8 +2821,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2858,8 +2922,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,204 +3023,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-216000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-160000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-238000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-128000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-114000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-53000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-67000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-71000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-25000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-42000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-68000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-27000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-29000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-21000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-45000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-35000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-74000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-36000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-46000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-22000</v>
       </c>
       <c r="AD32" s="3">
         <v>-22000</v>
       </c>
       <c r="AE32" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1681000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1743000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1589000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2160000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1302000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1466000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1364000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1868000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1353000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1299000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1324000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1670000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1220000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>951000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1166000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1389000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>838000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>931000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>844000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1097000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>906000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>889000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>767000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1043000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>750000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>701000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>640000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>919000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>700000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>515000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>545000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3250,209 +3326,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1681000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1743000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1589000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2160000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1302000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1466000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1364000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1868000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1353000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1299000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1324000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1670000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1220000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>951000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1166000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1389000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>838000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>931000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>844000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1097000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>906000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>889000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>767000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1043000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>750000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>701000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>640000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>919000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>700000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>515000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>545000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45424</v>
+      </c>
+      <c r="E38" s="2">
         <v>45340</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45256</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45172</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45053</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44969</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44885</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44801</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44689</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44605</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44521</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44437</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44325</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44241</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44157</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44073</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43961</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43877</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43793</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43709</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43597</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43513</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43429</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43345</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43233</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43149</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43065</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42981</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42862</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42778</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42694</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,8 +3572,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3523,596 +3609,615 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10404000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9095000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17011000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13700000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12493000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12970000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10856000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10203000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11193000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11819000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12751000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11258000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10226000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8637000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13590000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12277000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10826000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7786000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9027000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8384000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7013000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6080000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6778000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6055000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5877000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4781000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5689000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4546000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4538000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4744000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4805000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3379000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1095000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1226000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>853000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1534000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1215000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>735000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>817000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>846000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>638000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>477000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>725000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>917000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>900000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>617000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>833000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1028000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>948000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>929000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>993000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1060000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1154000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1042000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1175000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1204000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1167000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1049000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1196000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1233000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1187000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1221000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1311000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1350000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2583000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2779000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2542000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2285000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2502000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2714000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2312000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2241000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1991000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2232000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1932000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1803000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1595000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1934000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1646000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1550000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1507000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1988000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1711000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1535000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1704000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1995000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1795000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1669000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1593000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2001000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1559000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1432000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1462000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1597000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1498000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1252000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17430000</v>
+      </c>
+      <c r="E44" s="3">
         <v>17075000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>18001000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16651000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16324000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16081000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18571000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17907000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17623000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>16485000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16942000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14215000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13975000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13865000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>14901000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12242000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>11010000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>11850000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>13818000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>11395000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>11304000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>11356000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>12205000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>11040000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>10626000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>10671000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>11213000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>9834000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>9736000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>9530000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>10721000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>8969000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1776000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1971000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1673000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1709000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1755000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1830000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1594000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1499000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1563000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1552000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1500000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1312000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1220000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1255000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1126000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1023000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>963000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1150000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1094000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1111000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1110000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1175000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1001000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>321000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>430000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>397000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>240000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>272000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>333000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>368000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>235000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>268000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33288000</v>
+      </c>
+      <c r="E46" s="3">
         <v>32146000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40080000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35879000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>34289000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>34330000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34150000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>32696000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>33008000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>32565000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>33850000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29505000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27916000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>26308000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>32096000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>28120000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25254000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>23703000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>26643000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>23485000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>22285000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>21648000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>22954000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>20289000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19693000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18899000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>19897000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17317000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17256000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17460000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>18570000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>15218000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4209,106 +4314,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30705000</v>
+      </c>
+      <c r="E48" s="3">
         <v>30341000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29840000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29397000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28737000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28583000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>27931000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>27420000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26874000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26892000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26790000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26382000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26052000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25418000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25073000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25187000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24276000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24077000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>23834000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20890000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20475000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20145000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19879000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19681000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19178000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19049000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18682000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18161000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17535000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17342000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17156000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17043000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4318,11 +4429,11 @@
       <c r="E49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3">
         <v>994000</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>8</v>
@@ -4342,26 +4453,26 @@
       <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N49" s="3">
+      <c r="N49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O49" s="3">
         <v>1290000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1234000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1235000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1217000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1271000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1242000</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>8</v>
@@ -4378,8 +4489,8 @@
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -4405,8 +4516,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4503,8 +4617,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4601,106 +4718,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3918000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3836000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3803000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2724000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3726000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3935000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3946000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4050000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3970000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3621000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3509000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2091000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2072000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1957000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1831000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>978000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>960000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1002000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>954000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1025000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>992000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1006000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>981000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>860000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>734000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>755000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>799000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>869000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>840000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>828000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>806000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>902000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4797,106 +4920,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>67911000</v>
+      </c>
+      <c r="E54" s="3">
         <v>66323000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73723000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>68994000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>66752000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66848000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>66027000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>64166000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>63852000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>63078000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>64149000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>59268000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57274000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>54918000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>60217000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>55556000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>51732000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>48782000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>51431000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>45400000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>43752000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>42799000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>43814000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>40830000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>39605000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>38703000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>39378000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>36347000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>35631000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>35630000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>36532000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33163000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5060,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4967,596 +5097,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18844000</v>
+      </c>
+      <c r="E57" s="3">
         <v>17494000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20357000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17483000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16853000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16407000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18348000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17848000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17651000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17089000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19561000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16278000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15538000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14383000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17014000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14172000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10813000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11072000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14440000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11679000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11331000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10711000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13133000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11237000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10705000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10061000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11992000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9608000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9425000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8764000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11003000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>7612000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1080000</v>
+        <v>1077000</v>
       </c>
       <c r="E58" s="3">
         <v>1080000</v>
       </c>
       <c r="F58" s="3">
+        <v>1080000</v>
+      </c>
+      <c r="G58" s="3">
         <v>1081000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>76000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>71000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>73000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>77000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
-        <v>799000</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>799000</v>
       </c>
       <c r="O58" s="3">
+        <v>799000</v>
+      </c>
+      <c r="P58" s="3">
         <v>92000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>95000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>96000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>126000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1526000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>518000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1712000</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1699000</v>
       </c>
       <c r="W58" s="3">
         <v>1699000</v>
       </c>
       <c r="X58" s="3">
+        <v>1699000</v>
+      </c>
+      <c r="Y58" s="3">
         <v>1698000</v>
       </c>
-      <c r="Y58" s="3" t="s">
+      <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>90000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>119000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>122000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>116000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>86000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1158000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2257000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1159000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1100000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15440000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16114000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15331000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15019000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14855000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16033000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14648000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14077000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14117000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14456000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12982000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12364000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12352000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12086000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15557000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10546000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10440000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11105000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10113000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9859000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9802000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10041000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9340000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8599000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8587000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8730000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8252000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7801000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10811000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7839000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6999000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6863000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35361000</v>
+      </c>
+      <c r="E60" s="3">
         <v>34688000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36768000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33583000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31708000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32516000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33067000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31998000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31845000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31545000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33342000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29441000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27982000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26564000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32667000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24844000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22779000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22695000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>26265000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23237000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>22832000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>22450000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>22473000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19926000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19411000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>18913000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>20360000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17495000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>21394000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18860000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>19161000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15575000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5834000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5865000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5866000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5377000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6497000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6506000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6472000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6484000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6507000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6658000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6667000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6692000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7495000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7522000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7529000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8171000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8227000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5643000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5495000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5124000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4799000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4794000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6480000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6487000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6492000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6505000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6478000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6573000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2821000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2815000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3933000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4061000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4945000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5010000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4942000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4976000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4974000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5027000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5012000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5037000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4987000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4899000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5140000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5057000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4823000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4703000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4712000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3836000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3523000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3445000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3447000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1455000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1301000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1372000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1382000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1314000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1255000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1232000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1184000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1200000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1231000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1243000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1207000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1195000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5653,8 +5802,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5751,8 +5903,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5849,106 +6004,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46140000</v>
+      </c>
+      <c r="E66" s="3">
         <v>45563000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47576000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>43936000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43184000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44054000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44556000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43524000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43884000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43660000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45686000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41704000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>40792000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39266000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45357000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37272000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34930000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32168000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35570000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>30157000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>29266000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>28941000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>30647000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28031000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>27462000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26949000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>28300000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>25569000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>25733000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23190000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24559000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>21084000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5983,8 +6144,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6081,8 +6243,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6179,8 +6344,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6277,8 +6445,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6375,106 +6546,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15989000</v>
+      </c>
+      <c r="E72" s="3">
         <v>14980000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20499000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19521000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18035000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17341000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16412000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15585000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14294000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13474000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12606000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11666000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10466000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9766000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9232000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12879000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11883000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11384000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10787000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10258000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9496000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8916000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8387000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7887000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7176000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6727000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6300000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5988000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5508000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>8140000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>7882000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>7686000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6748,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6669,8 +6849,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6767,106 +6950,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21771000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20760000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26147000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25058000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23568000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22794000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21471000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20642000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19968000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19418000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18463000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17564000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16482000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15652000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14860000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18284000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16802000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16614000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15861000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15243000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14486000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13858000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13167000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12799000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12143000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11754000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11078000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10778000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9898000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12440000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11973000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12079000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6963,209 +7152,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45424</v>
+      </c>
+      <c r="E80" s="2">
         <v>45340</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45256</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45172</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45053</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44969</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44885</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44801</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44689</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44605</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44521</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44437</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44325</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44241</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44157</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44073</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43961</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43877</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43793</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43709</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43597</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43513</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43429</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43345</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43233</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43149</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43065</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42981</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42862</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42778</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42694</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1681000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1743000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1589000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2160000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1302000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1466000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1364000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1868000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1353000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1299000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1324000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1670000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1220000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>951000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1166000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1389000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>838000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>931000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>844000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1097000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>906000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>889000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>767000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1043000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>750000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>701000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>640000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>919000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>700000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>515000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>545000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7200,106 +7398,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>516000</v>
+      </c>
+      <c r="E83" s="3">
         <v>514000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>501000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>688000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>472000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>470000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>447000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>594000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>438000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>436000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>432000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>559000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>402000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>416000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>404000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>505000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>382000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>389000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>369000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>473000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>336000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>352000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>331000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>431000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>327000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>344000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>335000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>441000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>320000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>312000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>297000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7396,8 +7598,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7494,8 +7699,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7592,8 +7800,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7690,8 +7901,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7788,106 +8002,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2999000</v>
+      </c>
+      <c r="E89" s="3">
         <v>731000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4651000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3725000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1541000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3192000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2610000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2506000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1227000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>401000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3258000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2940000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3333000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>38000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2647000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4242000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1898000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>619000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2102000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2293000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2105000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-219000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2177000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1554000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2105000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>109000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2006000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1834000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1606000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>493000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2793000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-169000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7922,106 +8142,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1062000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1031000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1040000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1556000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-820000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-890000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1057000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1259000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-854000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-723000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1055000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1094000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1028000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-573000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-893000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-852000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-698000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-545000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-715000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-672000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-587000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-730000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1056000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-585000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-508000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-820000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-779000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-540000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-516000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-667000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-849000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8118,8 +8342,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8216,106 +8443,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-954000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-366000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-808000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1057000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1487000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-481000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-912000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1155000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1343000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-355000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-682000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-941000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1850000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-470000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-630000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-920000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-774000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-434000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-737000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1095000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-785000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-816000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-498000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-397000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-655000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1025000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8350,106 +8583,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-515000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-7107000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-905000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-452000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-399000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>-400000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-797000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-351000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-350000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-698000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-310000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-4430000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-310000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-619000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-287000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-573000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-286000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-251000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-501000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-250000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-219000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-220000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-3508000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-198000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-198000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-394000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8546,8 +8783,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8644,8 +8884,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8742,298 +8985,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-698000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7276000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-974000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-664000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-735000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-352000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-863000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1940000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-676000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-828000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-839000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-719000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-419000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4650000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-700000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1918000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2999000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1392000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-836000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-397000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-49000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-700000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-267000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-690000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-165000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-660000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-331000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E101" s="3">
         <v>15000</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-29000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>82000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-37000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-69000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-142000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-24000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-34000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>18000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>14000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>48000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>68000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-7000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-1000</v>
       </c>
       <c r="W101" s="3">
         <v>-1000</v>
       </c>
       <c r="X101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y101" s="3">
         <v>4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>46000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>67000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-52000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1309000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7916000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3311000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1207000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-477000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2114000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>653000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-990000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-626000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-932000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1493000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1032000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1589000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4953000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1313000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1451000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3040000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1241000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>643000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1371000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>933000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-698000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>723000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>178000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1096000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-908000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1143000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>8000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-206000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1426000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1505000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>COST</t>
   </si>
@@ -656,452 +656,465 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45536</v>
+      </c>
+      <c r="E7" s="2">
         <v>45424</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45340</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45256</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45172</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45053</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44969</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44885</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44801</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44689</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44605</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44521</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44437</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44325</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44241</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44157</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44073</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43961</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43877</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43793</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43709</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43597</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43513</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43429</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43345</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43233</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43149</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43065</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42981</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42862</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42778</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42694</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>79697000</v>
+      </c>
+      <c r="E8" s="3">
         <v>58515000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>58442000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>57799000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>78939000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>53648000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>55266000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>54437000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>72091000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>52596000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>51904000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>50363000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>62675000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>45277000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>44769000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>43208000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>53383000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37266000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>39072000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>37040000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>47498000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34740000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>35396000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>35069000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>44411000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32361000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>32995000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>31809000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>42300000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>28860000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>29766000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>28099000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>36560000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>69588000</v>
+      </c>
+      <c r="E9" s="3">
         <v>51173000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>51140000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>50457000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>69219000</v>
       </c>
-      <c r="H9" s="3">
-        <v>47175000</v>
-      </c>
       <c r="I9" s="3">
+        <v>46877000</v>
+      </c>
+      <c r="J9" s="3">
         <v>48423000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>47769000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>63558000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>46355000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>45517000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>43952000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>54733000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39415000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39078000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>37458000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>46337000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>32205000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>34056000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>32233000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>41310000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>30233000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>30720000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>30623000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>38671000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>28131000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>28733000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>27617000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>36697000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>24970000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>25927000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>24288000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>31649000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10109000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7342000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7302000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7342000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9720000</v>
       </c>
-      <c r="H10" s="3">
-        <v>6473000</v>
-      </c>
       <c r="I10" s="3">
+        <v>6771000</v>
+      </c>
+      <c r="J10" s="3">
         <v>6843000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6668000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8533000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6241000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6387000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6411000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7942000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5862000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5691000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5750000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7046000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5061000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5016000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4807000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6188000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4507000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4676000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4446000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5740000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4230000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4262000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4192000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5603000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3890000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3839000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3811000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4911000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1137,8 +1150,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1238,8 +1252,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1339,8 +1356,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1356,17 +1376,17 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>298000</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1375,28 +1395,28 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>118000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>84000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>57000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>246000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>212000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>370000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>302000</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1413,8 +1433,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1440,37 +1460,40 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>706000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>516000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>514000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>501000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>688000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>472000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>470000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
@@ -1490,20 +1513,20 @@
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T15" s="3">
         <v>16000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>4000</v>
       </c>
       <c r="V15" s="3">
         <v>4000</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>8</v>
+      <c r="W15" s="3">
+        <v>4000</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
@@ -1520,8 +1543,8 @@
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1541,8 +1564,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1575,210 +1601,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>76655000</v>
+      </c>
+      <c r="E17" s="3">
         <v>56318000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>56380000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>55815000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>76158000</v>
       </c>
-      <c r="H17" s="3">
-        <v>51969000</v>
-      </c>
       <c r="I17" s="3">
+        <v>51671000</v>
+      </c>
+      <c r="J17" s="3">
         <v>53363000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>52686000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>69594000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>50805000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50092000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>48670000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>60400000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>43614000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>43429000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>41778000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>51454000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>36087000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>37806000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>35979000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>46035000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>33618000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>34193000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>34120000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>42965000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>31294000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>31979000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>30858000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>40850000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>27892000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>28922000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>27250000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>35369000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3042000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2197000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2062000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1984000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2781000</v>
       </c>
-      <c r="H18" s="3">
-        <v>1679000</v>
-      </c>
       <c r="I18" s="3">
+        <v>1977000</v>
+      </c>
+      <c r="J18" s="3">
         <v>1903000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1751000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2497000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1791000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1812000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1693000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2275000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1663000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1340000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1430000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1929000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1179000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1266000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1061000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1463000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1122000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1203000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>949000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1446000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1067000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1016000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>951000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1450000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>968000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>844000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>849000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1191000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1814,287 +1847,294 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>128000</v>
+        <v>18000</v>
       </c>
       <c r="E20" s="3">
-        <v>216000</v>
+        <v>-34000</v>
       </c>
       <c r="F20" s="3">
-        <v>160000</v>
+        <v>-69000</v>
       </c>
       <c r="G20" s="3">
-        <v>238000</v>
+        <v>-6000</v>
       </c>
       <c r="H20" s="3">
-        <v>128000</v>
+        <v>-37000</v>
       </c>
       <c r="I20" s="3">
-        <v>114000</v>
+        <v>-18000</v>
       </c>
       <c r="J20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K20" s="3">
         <v>53000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>67000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>71000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>42000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>68000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>27000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>19000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>29000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>21000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>45000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>35000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>74000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>36000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>46000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>22000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>51000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>41000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>22000</v>
       </c>
       <c r="AE20" s="3">
         <v>22000</v>
       </c>
       <c r="AF20" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>18000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>26000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2841000</v>
+        <v>3730000</v>
       </c>
       <c r="E21" s="3">
-        <v>2792000</v>
+        <v>2747000</v>
       </c>
       <c r="F21" s="3">
         <v>2645000</v>
       </c>
       <c r="G21" s="3">
-        <v>3707000</v>
+        <v>2491000</v>
       </c>
       <c r="H21" s="3">
-        <v>2279000</v>
+        <v>3506000</v>
       </c>
       <c r="I21" s="3">
-        <v>2487000</v>
+        <v>2467000</v>
       </c>
       <c r="J21" s="3">
+        <v>2382000</v>
+      </c>
+      <c r="K21" s="3">
         <v>2251000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3158000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2300000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2273000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2167000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2902000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2092000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1775000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1863000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2425000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1582000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1700000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1465000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2010000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1494000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1601000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1302000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1928000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1435000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1367000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1308000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1913000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1152000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1172000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1628000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>41000</v>
+        <v>49000</v>
       </c>
       <c r="E22" s="3">
         <v>41000</v>
       </c>
       <c r="F22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="G22" s="3">
         <v>38000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>56000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>36000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>34000</v>
       </c>
       <c r="J22" s="3">
         <v>34000</v>
       </c>
       <c r="K22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="L22" s="3">
         <v>48000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>35000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>36000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>52000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>40000</v>
       </c>
       <c r="Q22" s="3">
         <v>40000</v>
       </c>
       <c r="R22" s="3">
+        <v>40000</v>
+      </c>
+      <c r="S22" s="3">
         <v>39000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>51000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>37000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>34000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>38000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>45000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>35000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>34000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>36000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>48000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>37000</v>
       </c>
       <c r="AC22" s="3">
         <v>37000</v>
@@ -2103,224 +2143,233 @@
         <v>37000</v>
       </c>
       <c r="AE22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>53000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>21000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>31000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>29000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3113000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2284000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2237000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2106000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2963000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1771000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1983000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1770000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2516000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1827000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1801000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1696000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2291000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1650000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1319000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1420000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1869000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1163000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1277000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1058000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1492000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1123000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1215000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>935000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1449000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1071000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>986000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>936000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1419000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>965000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>809000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>846000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1181000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E24" s="3">
         <v>603000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>494000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>517000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>803000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>469000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>517000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>406000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>638000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>455000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>481000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>351000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>597000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>417000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>348000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>239000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>465000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>311000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>330000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>202000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>340000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>280000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>377000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>185000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>402000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>310000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>247000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>285000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>487000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>259000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>288000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>291000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>396000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,210 +2469,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2354000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1681000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1743000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1589000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2160000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1302000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1466000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1364000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1878000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1372000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1320000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1345000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1694000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1233000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>971000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1181000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1404000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>852000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>947000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>856000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1152000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>843000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>838000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>750000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>761000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>739000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>651000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>932000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>706000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>521000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>555000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>785000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2354000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1681000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1743000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1589000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2160000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1302000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1466000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1364000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1868000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1353000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1299000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1324000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1670000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1220000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>951000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1166000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1389000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>838000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>931000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>844000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1139000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>833000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>826000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>740000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1037000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>749000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>727000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>640000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>919000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>700000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>515000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>545000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2723,8 +2781,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2764,8 +2825,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -2773,11 +2834,11 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
+      <c r="S29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2785,29 +2846,29 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>-42000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>73000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>63000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>27000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>6000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>1000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-26000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2824,8 +2885,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2925,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3026,210 +3093,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-128000</v>
+        <v>-18000</v>
       </c>
       <c r="E32" s="3">
-        <v>-216000</v>
+        <v>34000</v>
       </c>
       <c r="F32" s="3">
-        <v>-160000</v>
+        <v>69000</v>
       </c>
       <c r="G32" s="3">
-        <v>-238000</v>
+        <v>6000</v>
       </c>
       <c r="H32" s="3">
-        <v>-128000</v>
+        <v>37000</v>
       </c>
       <c r="I32" s="3">
-        <v>-114000</v>
+        <v>18000</v>
       </c>
       <c r="J32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-53000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-67000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-71000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-42000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-68000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-19000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-29000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-21000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-45000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-35000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-74000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-22000</v>
       </c>
       <c r="AE32" s="3">
         <v>-22000</v>
       </c>
       <c r="AF32" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>4000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2354000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1681000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1743000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1589000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2160000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1302000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1466000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1364000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1868000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1353000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1299000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1324000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1670000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1220000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>951000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1166000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1389000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>838000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>931000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>844000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1097000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>906000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>889000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>767000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1043000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>750000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>701000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>640000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>919000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>700000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>515000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>545000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3329,215 +3405,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2354000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1681000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1743000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1589000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2160000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1302000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1466000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1364000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1868000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1353000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1299000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1324000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1670000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1220000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>951000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1166000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1389000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>838000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>931000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>844000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1097000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>906000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>889000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>767000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1043000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>750000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>701000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>640000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>919000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>700000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>515000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>545000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45536</v>
+      </c>
+      <c r="E38" s="2">
         <v>45424</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45340</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45256</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45172</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45053</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44969</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44885</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44801</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44689</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44605</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44521</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44437</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44325</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44241</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44157</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44073</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43961</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43877</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43793</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43709</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43597</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43513</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43429</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43345</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43233</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43149</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43065</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42981</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42862</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42778</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42694</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3573,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,637 +3696,656 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9906000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10404000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9095000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17011000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13700000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12493000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12970000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10856000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10203000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11193000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11819000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12751000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11258000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10226000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8637000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13590000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12277000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10826000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7786000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9027000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8384000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7013000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6080000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6778000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6055000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5877000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4781000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5689000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4546000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4538000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4744000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4805000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3379000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1238000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1095000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1226000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>853000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1534000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1215000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>735000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>817000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>846000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>638000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>477000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>725000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>917000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>900000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>617000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>833000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1028000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>948000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>929000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>993000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1060000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1154000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1042000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1175000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1204000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1167000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1049000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1196000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1233000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1187000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1221000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1311000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1350000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2721000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2583000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2779000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2542000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2285000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2502000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2714000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2312000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2241000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1991000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2232000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1932000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1803000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1595000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1934000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1646000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1550000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1507000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1988000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1711000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1535000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1704000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1995000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1795000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1669000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1593000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2001000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1559000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1432000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1462000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1597000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1498000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1252000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18647000</v>
+      </c>
+      <c r="E44" s="3">
         <v>17430000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17075000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18001000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16651000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16324000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16081000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18571000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17907000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>17623000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16485000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>16942000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14215000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13975000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13865000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>14901000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12242000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>11010000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>11850000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>13818000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>11395000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>11304000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>11356000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>12205000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>11040000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>10626000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>10671000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>11213000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>9834000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>9736000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>9530000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>10721000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>8969000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1734000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1776000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1971000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1673000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1709000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1755000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1830000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1594000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1499000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1563000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1552000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1312000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1220000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1255000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1126000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1023000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>963000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1150000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1094000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1111000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1110000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1175000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1001000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>321000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>430000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>397000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>240000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>272000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>333000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>368000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>235000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>268000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34246000</v>
+      </c>
+      <c r="E46" s="3">
         <v>33288000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32146000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>40080000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35879000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>34289000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34330000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>34150000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>32696000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33008000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32565000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>33850000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29505000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>27916000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>26308000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>32096000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>28120000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>25254000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>23703000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>26643000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>23485000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>22285000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21648000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>22954000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>20289000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>19693000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18899000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>19897000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17317000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17256000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17460000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>18570000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15218000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4317,132 +4422,138 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33082000</v>
+      </c>
+      <c r="E48" s="3">
         <v>30705000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30341000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29840000</v>
       </c>
-      <c r="G48" s="3">
-        <v>29397000</v>
-      </c>
       <c r="H48" s="3">
+        <v>30722000</v>
+      </c>
+      <c r="I48" s="3">
         <v>28737000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28583000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>27931000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>27420000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26874000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26892000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26790000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26382000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26052000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25418000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25073000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>25187000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24276000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24077000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23834000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20890000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20475000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20145000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19879000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19681000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19178000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19049000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18682000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18161000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17535000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17342000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17156000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>17043000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>8</v>
+      <c r="D49" s="3">
+        <v>994000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>994000</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
@@ -4456,26 +4567,26 @@
       <c r="N49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O49" s="3">
+      <c r="O49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P49" s="3">
         <v>1290000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1234000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1235000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1217000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1271000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1242000</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>8</v>
@@ -4492,8 +4603,8 @@
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -4519,8 +4630,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4620,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4721,109 +4838,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>961000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3918000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3836000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3803000</v>
       </c>
-      <c r="G52" s="3">
-        <v>2724000</v>
-      </c>
       <c r="H52" s="3">
+        <v>908000</v>
+      </c>
+      <c r="I52" s="3">
         <v>3726000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3935000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3946000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4050000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3970000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3621000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3509000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2091000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2072000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1957000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1831000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>978000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>960000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1002000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>954000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1025000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>992000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1006000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>981000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>860000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>734000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>755000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>799000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>869000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>840000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>828000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>806000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>902000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4923,109 +5046,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>69831000</v>
+      </c>
+      <c r="E54" s="3">
         <v>67911000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>66323000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73723000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>68994000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66752000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>66848000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>66027000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64166000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>63852000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>63078000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>64149000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>59268000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57274000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>54918000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>60217000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>55556000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>51732000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>48782000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>51431000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>45400000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>43752000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>42799000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>43814000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>40830000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>39605000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>38703000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>39378000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>36347000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>35631000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>35630000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>36532000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>33163000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5061,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5098,614 +5228,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19421000</v>
+      </c>
+      <c r="E57" s="3">
         <v>18844000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17494000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20357000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17483000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16853000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16407000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18348000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17848000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17651000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17089000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19561000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16278000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15538000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14383000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17014000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14172000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10813000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11072000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14440000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11679000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11331000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10711000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13133000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11237000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10705000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10061000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11992000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9608000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9425000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8764000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11003000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>7612000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1077000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1080000</v>
       </c>
       <c r="F58" s="3">
         <v>1080000</v>
       </c>
       <c r="G58" s="3">
-        <v>1081000</v>
+        <v>1080000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1430000</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>76000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>71000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>73000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>77000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
-        <v>799000</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>799000</v>
       </c>
       <c r="P58" s="3">
+        <v>799000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>92000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>95000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>96000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>126000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1526000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>518000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1712000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>1699000</v>
       </c>
       <c r="X58" s="3">
         <v>1699000</v>
       </c>
       <c r="Y58" s="3">
+        <v>1699000</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1698000</v>
       </c>
-      <c r="Z58" s="3" t="s">
+      <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>90000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>119000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>122000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>116000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>86000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1158000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2257000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1159000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1100000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15440000</v>
+        <v>8385000</v>
       </c>
       <c r="E59" s="3">
-        <v>16114000</v>
+        <v>8736000</v>
       </c>
       <c r="F59" s="3">
-        <v>15331000</v>
+        <v>9045000</v>
       </c>
       <c r="G59" s="3">
-        <v>15019000</v>
+        <v>8650000</v>
       </c>
       <c r="H59" s="3">
-        <v>14855000</v>
+        <v>8242000</v>
       </c>
       <c r="I59" s="3">
-        <v>16033000</v>
+        <v>8662000</v>
       </c>
       <c r="J59" s="3">
+        <v>9534000</v>
+      </c>
+      <c r="K59" s="3">
         <v>14648000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14077000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14117000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14456000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12982000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12364000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12352000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12086000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15557000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10546000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10440000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11105000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10113000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9859000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9802000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10041000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8599000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8587000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8730000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8252000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7801000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10811000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7839000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6999000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6863000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35464000</v>
+      </c>
+      <c r="E60" s="3">
         <v>35361000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34688000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36768000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33583000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>31708000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32516000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33067000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31998000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31845000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31545000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33342000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29441000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27982000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26564000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32667000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24844000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22779000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>22695000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26265000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>23237000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>22832000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>22450000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>22473000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19926000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19411000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>18913000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20360000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>17495000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>21394000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18860000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>19161000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>15575000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5834000</v>
+        <v>9520000</v>
       </c>
       <c r="E61" s="3">
-        <v>5865000</v>
+        <v>8220000</v>
       </c>
       <c r="F61" s="3">
-        <v>5866000</v>
+        <v>8353000</v>
       </c>
       <c r="G61" s="3">
-        <v>5377000</v>
+        <v>8267000</v>
       </c>
       <c r="H61" s="3">
-        <v>6497000</v>
+        <v>9106000</v>
       </c>
       <c r="I61" s="3">
-        <v>6506000</v>
+        <v>9004000</v>
       </c>
       <c r="J61" s="3">
+        <v>9063000</v>
+      </c>
+      <c r="K61" s="3">
         <v>6472000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6484000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6507000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6658000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6667000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6692000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7495000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7522000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7529000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8171000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8227000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5643000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5495000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5124000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4799000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4794000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6480000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6487000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6492000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6505000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6478000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6573000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2821000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2815000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3933000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4061000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4945000</v>
+        <v>456000</v>
       </c>
       <c r="E62" s="3">
-        <v>5010000</v>
+        <v>2559000</v>
       </c>
       <c r="F62" s="3">
-        <v>4942000</v>
+        <v>2522000</v>
       </c>
       <c r="G62" s="3">
-        <v>4976000</v>
+        <v>2541000</v>
       </c>
       <c r="H62" s="3">
-        <v>4974000</v>
+        <v>452000</v>
       </c>
       <c r="I62" s="3">
-        <v>5027000</v>
+        <v>2467000</v>
       </c>
       <c r="J62" s="3">
+        <v>2470000</v>
+      </c>
+      <c r="K62" s="3">
         <v>5012000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5037000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4987000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4899000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5140000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5057000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4823000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4703000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4712000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3836000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3523000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3445000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3447000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1455000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1301000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1372000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1382000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1314000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1255000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1232000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1184000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1200000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1231000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1243000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1207000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1195000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5805,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5906,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6007,109 +6162,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46209000</v>
+      </c>
+      <c r="E66" s="3">
         <v>46140000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45563000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47576000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43936000</v>
       </c>
-      <c r="H66" s="3">
-        <v>43184000</v>
-      </c>
       <c r="I66" s="3">
-        <v>44054000</v>
+        <v>43179000</v>
       </c>
       <c r="J66" s="3">
+        <v>44049000</v>
+      </c>
+      <c r="K66" s="3">
         <v>44556000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43524000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43884000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43660000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45686000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>41704000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40792000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39266000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45357000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37272000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34930000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32168000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>35570000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30157000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29266000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>28941000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>30647000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>28031000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>27462000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26949000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>28300000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>25569000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>25733000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23190000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24559000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>21084000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6145,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6246,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6347,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6549,109 +6720,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17619000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15989000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14980000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20499000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19521000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18035000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17341000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16412000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15585000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14294000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13474000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12606000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11666000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10466000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9766000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9232000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12879000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11883000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11384000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10787000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10258000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9496000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8916000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8387000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7887000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7176000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6727000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6300000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5988000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5508000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8140000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>7882000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>7686000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6751,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6852,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6953,109 +7136,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23622000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21771000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20760000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26147000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25058000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23568000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22794000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21471000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20642000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19968000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19418000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18463000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17564000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16482000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15652000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14860000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18284000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16802000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16614000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15861000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15243000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14486000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13858000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13167000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12799000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12143000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11754000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11078000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10778000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9898000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12440000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11973000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12079000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7155,215 +7344,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45536</v>
+      </c>
+      <c r="E80" s="2">
         <v>45424</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45340</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45256</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45172</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45053</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44969</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44885</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44801</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44689</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44605</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44521</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44437</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44325</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44241</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44157</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44073</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43961</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43877</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43793</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43709</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43597</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43513</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43429</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43345</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43233</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43149</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43065</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42981</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42862</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42778</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42694</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2354000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1681000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1743000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1589000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2160000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1302000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1466000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1364000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1868000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1353000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1299000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1324000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1670000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1220000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>951000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1166000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1389000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>838000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>931000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>844000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1097000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>906000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>889000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>767000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1043000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>750000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>701000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>640000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>919000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>700000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>515000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>545000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7399,109 +7597,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>516000</v>
+        <v>688000</v>
       </c>
       <c r="E83" s="3">
-        <v>514000</v>
+        <v>472000</v>
       </c>
       <c r="F83" s="3">
-        <v>501000</v>
+        <v>470000</v>
       </c>
       <c r="G83" s="3">
-        <v>688000</v>
+        <v>447000</v>
       </c>
       <c r="H83" s="3">
-        <v>472000</v>
+        <v>601000</v>
       </c>
       <c r="I83" s="3">
-        <v>470000</v>
+        <v>431000</v>
       </c>
       <c r="J83" s="3">
+        <v>436000</v>
+      </c>
+      <c r="K83" s="3">
         <v>447000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>594000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>438000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>436000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>432000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>559000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>402000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>416000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>404000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>505000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>382000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>389000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>369000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>473000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>336000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>352000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>331000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>431000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>327000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>344000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>335000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>441000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>320000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>312000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>297000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7601,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7702,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7803,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7904,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8005,109 +8219,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2958000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2999000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>731000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4651000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3725000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1541000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3192000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2610000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2506000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1227000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>401000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3258000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2940000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3333000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>38000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2647000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4242000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1898000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>619000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2102000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2293000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2105000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-219000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2177000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1554000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2105000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>109000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2006000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1834000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1606000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>493000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2793000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-169000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8143,109 +8363,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1577000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1031000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1040000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1556000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-820000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-890000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1057000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1259000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-854000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-723000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1055000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1094000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1028000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-573000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-893000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-852000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-698000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-545000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-715000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-672000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-587000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-730000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1056000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-585000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-508000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-820000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-779000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-540000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-516000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-667000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-849000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8345,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8446,109 +8673,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1703000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-954000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-366000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-808000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1057000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1487000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-481000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-912000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1155000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1343000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-355000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-682000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-941000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1850000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-470000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-630000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-920000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-774000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-434000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1095000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-785000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-816000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-498000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-397000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-655000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1025000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8584,109 +8817,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-515000</v>
+        <v>514000</v>
       </c>
       <c r="E96" s="3">
-        <v>-7107000</v>
+        <v>515000</v>
       </c>
       <c r="F96" s="3">
-        <v>-905000</v>
+        <v>452000</v>
       </c>
       <c r="G96" s="3">
-        <v>-452000</v>
+        <v>905000</v>
       </c>
       <c r="H96" s="3">
-        <v>-399000</v>
+        <v>452000</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>399000</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-400000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-797000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-351000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-350000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-698000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-310000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-4430000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-310000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-619000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-287000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-573000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-286000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-251000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-501000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-250000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-219000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-220000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-3508000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-198000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-198000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-394000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8786,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8887,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8988,307 +9231,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1816000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-698000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7276000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-974000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-664000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-735000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-352000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-863000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1940000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-676000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-828000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-839000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-719000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-419000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4650000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-700000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1918000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2999000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1392000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-836000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-397000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-49000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-700000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-267000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-690000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-165000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-660000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-331000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-38000</v>
+        <v>-29000</v>
       </c>
       <c r="E101" s="3">
-        <v>15000</v>
+        <v>-1000</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="G101" s="3">
-        <v>-29000</v>
+        <v>-37000</v>
       </c>
       <c r="H101" s="3">
-        <v>-1000</v>
+        <v>-69000</v>
       </c>
       <c r="I101" s="3">
-        <v>82000</v>
+        <v>-142000</v>
       </c>
       <c r="J101" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-37000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-69000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-142000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-24000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-14000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-34000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>18000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>14000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>48000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>68000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-1000</v>
       </c>
       <c r="X101" s="3">
         <v>-1000</v>
       </c>
       <c r="Y101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z101" s="3">
         <v>4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>46000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>67000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>8000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-52000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-498000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1309000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7916000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3311000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1207000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-477000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2114000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>653000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-990000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-626000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-932000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1493000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1032000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1589000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4953000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1313000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1451000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3040000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1241000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>643000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1371000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>933000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-698000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>723000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>178000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1096000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-908000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1143000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>8000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-206000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1426000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1505000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>COST</t>
   </si>
@@ -656,465 +656,491 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45704</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45620</v>
+      </c>
+      <c r="F7" s="2">
         <v>45536</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45424</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45340</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45256</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45172</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45053</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44969</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44885</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44801</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44689</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44605</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44521</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44437</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44325</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44241</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44157</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44073</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43961</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43877</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43793</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43709</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43597</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43513</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43429</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43345</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43233</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43149</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43065</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42981</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42862</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42778</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42694</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>63723000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>62151000</v>
+      </c>
+      <c r="F8" s="3">
         <v>79697000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>58515000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>58442000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>57799000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>78939000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>53648000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>55266000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>54437000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>72091000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>52596000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>51904000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>50363000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>62675000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>45277000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>44769000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>43208000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>53383000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>37266000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>39072000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>37040000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>47498000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>34740000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>35396000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>35069000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>44411000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>32361000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>32995000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>31809000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>42300000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>28860000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>29766000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>28099000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>36560000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>55744000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>54109000</v>
+      </c>
+      <c r="F9" s="3">
         <v>69588000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>51173000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>51140000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>50457000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>69219000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>46877000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>48423000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>47769000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>63558000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>46355000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>45517000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>43952000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>54733000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>39415000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>39078000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>37458000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>46337000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>32205000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>34056000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>32233000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>41310000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>30233000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>30720000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>30623000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>38671000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>28131000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>28733000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>27617000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>36697000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>24970000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>25927000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>24288000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>31649000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7979000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>8042000</v>
+      </c>
+      <c r="F10" s="3">
         <v>10109000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>7342000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>7302000</v>
       </c>
       <c r="G10" s="3">
         <v>7342000</v>
       </c>
       <c r="H10" s="3">
+        <v>7302000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>7342000</v>
+      </c>
+      <c r="J10" s="3">
         <v>9720000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>6771000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>6843000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>6668000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>8533000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>6241000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>6387000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6411000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>7942000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>5862000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>5691000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5750000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>7046000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>5061000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>5016000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>4807000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>6188000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>4507000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>4676000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>4446000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>5740000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>4230000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>4262000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>4192000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>5603000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>3890000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>3839000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>3811000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>4911000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1151,8 +1177,10 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1255,8 +1283,14 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1359,8 +1393,14 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1376,53 +1416,53 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>298000</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>118000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>84000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>57000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>246000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>212000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>370000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>302000</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1436,11 +1476,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1463,43 +1503,49 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>548000</v>
+      </c>
+      <c r="F15" s="3">
         <v>706000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>516000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>514000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>501000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>688000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>472000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>470000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
@@ -1516,23 +1562,23 @@
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3">
         <v>16000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>7000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>4000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>4000</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
@@ -1546,11 +1592,11 @@
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1567,8 +1613,14 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1602,216 +1654,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>61407000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>59955000</v>
+      </c>
+      <c r="F17" s="3">
         <v>76655000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>56318000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>56380000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>55815000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>76158000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>51671000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>53363000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>52686000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>69594000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>50805000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>50092000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>48670000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>60400000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>43614000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>43429000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>41778000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>51454000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>36087000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>37806000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>35979000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>46035000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>33618000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>34193000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>34120000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>42965000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>31294000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>31979000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>30858000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>40850000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>27892000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>28922000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>27250000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>35369000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2316000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2196000</v>
+      </c>
+      <c r="F18" s="3">
         <v>3042000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2197000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2062000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1984000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2781000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1977000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1903000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1751000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2497000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1791000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1812000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1693000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2275000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1663000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1340000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1430000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1929000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1179000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1266000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1061000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1463000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1122000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1203000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>949000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1446000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1067000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1016000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>951000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1450000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>968000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>844000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>849000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>1191000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1848,528 +1914,560 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="F20" s="3">
         <v>18000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-34000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-69000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-37000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-18000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-9000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>53000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>67000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>71000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>25000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>42000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>68000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>27000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>19000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>29000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-9000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>21000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>45000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>35000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>74000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>36000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>46000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>22000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>51000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>41000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>7000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>22000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>22000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>18000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2901000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2795000</v>
+      </c>
+      <c r="F21" s="3">
         <v>3730000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2747000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2645000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2491000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3506000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2467000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2382000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2251000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3158000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2300000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2273000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2167000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2902000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2092000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1775000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1863000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2425000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1582000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1700000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1465000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2010000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1494000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1601000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1302000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1928000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1435000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1367000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1308000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1913000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>1152000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1172000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>1628000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F22" s="3">
         <v>49000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>41000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>41000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>38000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>56000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>36000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>34000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>34000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>48000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>35000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>36000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>39000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>52000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>40000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>40000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>39000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>51000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>37000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>34000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>38000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>45000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>35000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>34000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>36000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>48000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>37000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>37000</v>
       </c>
       <c r="AE22" s="3">
         <v>37000</v>
       </c>
       <c r="AF22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>53000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>21000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>31000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>29000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2422000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2306000</v>
+      </c>
+      <c r="F23" s="3">
         <v>3113000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2284000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2237000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2106000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2963000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1771000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1983000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1770000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2516000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1827000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1801000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1696000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2291000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1650000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1319000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1420000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1869000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1163000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1277000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1058000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1492000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1123000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1215000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>935000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1449000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1071000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>986000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>936000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>1419000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>965000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>809000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>846000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>1181000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>634000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>508000</v>
+      </c>
+      <c r="F24" s="3">
         <v>759000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>603000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>494000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>517000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>803000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>469000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>517000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>406000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>638000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>455000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>481000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>351000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>597000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>417000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>348000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>239000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>465000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>311000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>330000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>202000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>340000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>280000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>377000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>185000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>402000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>310000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>247000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>285000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>487000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>259000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>288000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>291000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>396000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2472,216 +2570,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1788000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1798000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2354000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1681000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1743000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1589000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2160000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1302000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1466000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1364000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1878000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1372000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1320000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1345000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1694000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1233000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>971000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1181000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1404000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>852000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>947000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>856000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1152000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>843000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>838000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>750000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>761000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>739000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>651000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>932000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>706000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>521000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>555000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>785000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1788000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1798000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2354000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1681000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1743000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1589000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2160000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1302000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1466000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1364000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1868000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1353000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1299000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1324000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1670000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1220000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>951000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1166000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1389000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>838000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>931000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>844000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1139000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>833000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>826000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>740000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1037000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>749000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>727000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>640000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>919000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>700000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>515000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>545000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,8 +2900,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2828,53 +2950,53 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>73000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>63000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>27000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>6000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>1000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>-26000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2888,8 +3010,14 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2992,8 +3120,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3096,216 +3230,234 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>51000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-18000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>34000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>69000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>37000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>18000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>9000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-53000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-67000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-71000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-25000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-42000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-27000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-19000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-29000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>9000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-21000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-45000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-35000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-74000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-36000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>4000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1788000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1798000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2354000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1681000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1743000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1589000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2160000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1302000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1466000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1364000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1868000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1353000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1299000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1324000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1670000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1220000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>951000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1166000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1389000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>838000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>931000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>844000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1097000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>906000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>889000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>767000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1043000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>750000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>701000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>640000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>919000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>700000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>515000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>545000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3408,221 +3560,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1788000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1798000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2354000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1681000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1743000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1589000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2160000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1302000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1466000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1364000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1868000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1353000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1299000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1324000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1670000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1220000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>951000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1166000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1389000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>838000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>931000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>844000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1097000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>906000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>889000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>767000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1043000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>750000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>701000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>640000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>919000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>700000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>515000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>545000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45704</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45620</v>
+      </c>
+      <c r="F38" s="2">
         <v>45536</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45424</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45340</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45256</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45172</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45053</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44969</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44885</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44801</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44689</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44605</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44521</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44437</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44325</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44241</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44157</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44073</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43961</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43877</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43793</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43709</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43597</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43513</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43429</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43345</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43233</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43149</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43065</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42981</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42862</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42778</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42694</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3659,8 +3829,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3697,632 +3869,670 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12356000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10907000</v>
+      </c>
+      <c r="F41" s="3">
         <v>9906000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10404000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9095000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>17011000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>13700000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>12493000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12970000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10856000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10203000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11193000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>11819000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12751000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>11258000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>10226000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>8637000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>13590000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>12277000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>10826000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>7786000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>9027000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>8384000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>7013000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>6080000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>6778000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>6055000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>5877000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>4781000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>5689000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>4546000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>4538000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>4744000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>4805000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>3379000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>802000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>920000</v>
+      </c>
+      <c r="F42" s="3">
         <v>1238000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1095000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1226000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>853000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1534000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1215000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>735000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>817000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>846000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>638000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>477000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>725000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>917000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>900000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>617000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>833000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1028000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>948000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>929000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>993000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1060000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1154000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1042000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1175000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1204000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1167000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1049000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1196000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>1233000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>1187000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>1221000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>1311000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>1350000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3060000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2963000</v>
+      </c>
+      <c r="F43" s="3">
         <v>2721000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2583000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2779000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2542000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2285000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2502000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2714000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2312000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2241000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1991000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2232000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1932000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1803000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1595000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1934000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1646000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1550000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1507000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1988000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1711000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1535000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1704000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1995000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1795000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1669000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1593000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>2001000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>1559000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1432000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>1462000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>1597000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>1498000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>1252000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18754000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>20979000</v>
+      </c>
+      <c r="F44" s="3">
         <v>18647000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>17430000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>17075000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>18001000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>16651000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>16324000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>16081000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>18571000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>17907000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>17623000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>16485000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>16942000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>14215000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>13975000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>13865000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>14901000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>12242000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>11010000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>11850000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>13818000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>11395000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>11304000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>11356000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>12205000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>11040000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>10626000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>10671000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>11213000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>9834000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>9736000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>9530000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>10721000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>8969000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1925000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1754000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1734000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1776000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1971000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1673000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1709000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1755000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1830000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1594000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1499000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1563000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1552000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1500000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1312000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1220000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1255000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1126000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1023000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>963000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1150000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1094000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1111000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1110000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1175000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1001000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>321000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>430000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>397000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>240000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>272000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>333000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>368000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>235000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>268000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36897000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>37523000</v>
+      </c>
+      <c r="F46" s="3">
         <v>34246000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>33288000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>32146000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>40080000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>35879000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>34289000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>34330000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>34150000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>32696000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>33008000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>32565000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>33850000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>29505000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>27916000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>26308000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>32096000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>28120000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>25254000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>23703000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>26643000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>23485000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>22285000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>21648000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>22954000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>20289000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>19693000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>18899000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>19897000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>17317000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>17256000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>17460000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>18570000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>15218000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4347,11 +4557,11 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4425,141 +4635,153 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32340000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>31875000</v>
+      </c>
+      <c r="F48" s="3">
         <v>33082000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>30705000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>30341000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>29840000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>30722000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>28737000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>28583000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>27931000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>27420000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>26874000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>26892000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>26790000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>26382000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>26052000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>25418000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>25073000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>25187000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>24276000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>24077000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>23834000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>20890000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>20475000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>20145000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>19879000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>19681000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>19178000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>19049000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>18682000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>18161000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>17535000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>17342000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>17156000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>17043000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>994000</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>994000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
@@ -4570,29 +4792,29 @@
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3">
+      <c r="P49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R49" s="3">
         <v>1290000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1234000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1235000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1217000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1271000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1242000</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>8</v>
@@ -4606,11 +4828,11 @@
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4633,8 +4855,14 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4737,8 +4965,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4841,112 +5075,124 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3987000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3988000</v>
+      </c>
+      <c r="F52" s="3">
         <v>961000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3918000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3836000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3803000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>908000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3726000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3935000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3946000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>4050000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3970000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3621000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3509000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2091000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2072000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1957000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1831000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>978000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>960000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1002000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>954000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1025000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>992000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1006000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>981000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>860000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>734000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>755000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>799000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>869000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>840000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>828000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>806000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>902000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5049,112 +5295,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73224000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>73386000</v>
+      </c>
+      <c r="F54" s="3">
         <v>69831000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>67911000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>66323000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>73723000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>68994000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>66752000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>66848000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>66027000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>64166000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>63852000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>63078000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>64149000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>59268000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>57274000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>54918000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>60217000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>55556000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>51732000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>48782000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>51431000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>45400000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>43752000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>42799000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>43814000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>40830000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>39605000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>38703000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>39378000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>36347000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>35631000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>35630000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>36532000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>33163000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5191,8 +5449,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5229,632 +5489,670 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18610000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>21793000</v>
+      </c>
+      <c r="F57" s="3">
         <v>19421000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>18844000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>17494000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>20357000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>17483000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>16853000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>16407000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>18348000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>17848000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>17651000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>17089000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>19561000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>16278000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>15538000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>14383000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>17014000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>14172000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>10813000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>11072000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>14440000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>11679000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>11331000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>10711000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>13133000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>11237000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>10705000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>10061000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>11992000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>9608000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>9425000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>8764000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>11003000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>7612000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>97000</v>
+      </c>
+      <c r="F58" s="3">
         <v>429000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1077000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1080000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1080000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1430000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>76000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>71000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>73000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>77000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>799000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>799000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>92000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>95000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>96000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>126000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1526000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>518000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1712000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1699000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1699000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1698000</v>
       </c>
-      <c r="AA58" s="3" t="s">
+      <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>90000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>119000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>122000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>116000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>86000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1158000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>2257000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>1159000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>1100000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10748000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>9170000</v>
+      </c>
+      <c r="F59" s="3">
         <v>8385000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>8736000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>9045000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>8650000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>8242000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>8662000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>9534000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>14648000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>14077000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>14117000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>14456000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12982000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>12364000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>12352000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>12086000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>15557000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>10546000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>10440000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>11105000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>10113000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>9859000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>9802000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>10041000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>8599000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>8587000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>8730000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>8252000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>7801000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>10811000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>7839000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>6999000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>6863000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36999000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>38289000</v>
+      </c>
+      <c r="F60" s="3">
         <v>35464000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>35361000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>34688000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>36768000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>33583000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>31708000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>32516000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>33067000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>31998000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>31845000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>31545000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>33342000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>29441000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>27982000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>26564000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>32667000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>24844000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>22779000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>22695000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>26265000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>23237000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>22832000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>22450000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>22473000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>19926000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>19411000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>18913000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>20360000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>17495000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>21394000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>18860000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>19161000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>15575000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8039000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8033000</v>
+      </c>
+      <c r="F61" s="3">
         <v>9520000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>8220000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>8353000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>8267000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>9106000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>9004000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>9063000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6472000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6484000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6507000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6658000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6667000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>6692000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>7495000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>7522000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7529000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>8171000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>8227000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>5643000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>5495000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>5124000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>4799000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4794000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>6480000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>6487000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>6492000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>6505000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>6478000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>6573000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2821000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>2815000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>3933000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>4061000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2609000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2613000</v>
+      </c>
+      <c r="F62" s="3">
         <v>456000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2559000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2522000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2541000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>452000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2467000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2470000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5012000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5037000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4987000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4899000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>5140000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>5057000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4823000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4703000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4712000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3836000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3523000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3445000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3447000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1455000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1301000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1372000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1382000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1314000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1255000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1232000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1184000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1200000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1231000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1243000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1207000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1195000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5957,8 +6255,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6061,8 +6365,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6165,112 +6475,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47647000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>48935000</v>
+      </c>
+      <c r="F66" s="3">
         <v>46209000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>46140000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>45563000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>47576000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>43936000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>43179000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>44049000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>44556000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>43524000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>43884000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>43660000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>45686000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>41704000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>40792000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>39266000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>45357000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>37272000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>34930000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>32168000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>35570000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>30157000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>29266000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>28941000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>30647000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>28031000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>27462000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>26949000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>28300000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>25569000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>25733000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>23190000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>24559000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>21084000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6307,8 +6629,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6411,8 +6735,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6515,8 +6845,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6619,8 +6955,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6723,112 +7065,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19770000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>18700000</v>
+      </c>
+      <c r="F72" s="3">
         <v>17619000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>15989000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>14980000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>20499000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>19521000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>18035000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>17341000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>16412000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>15585000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>14294000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>13474000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>12606000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>11666000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>10466000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>9766000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>9232000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>12879000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>11883000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>11384000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>10787000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>10258000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>9496000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>8916000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>8387000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>7887000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>7176000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>6727000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>6300000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>5988000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>5508000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>8140000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>7882000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>7686000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6931,8 +7285,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7035,8 +7395,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7139,112 +7505,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25577000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>24451000</v>
+      </c>
+      <c r="F76" s="3">
         <v>23622000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>21771000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20760000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>26147000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>25058000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>23568000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>22794000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>21471000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>20642000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19968000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>19418000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>18463000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>17564000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>16482000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>15652000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>14860000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>18284000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>16802000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>16614000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>15861000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>15243000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>14486000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>13858000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>13167000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>12799000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>12143000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>11754000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>11078000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>10778000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>9898000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>12440000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>11973000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>12079000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7347,221 +7725,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45704</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45620</v>
+      </c>
+      <c r="F80" s="2">
         <v>45536</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45424</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45340</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45256</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45172</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45053</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44969</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44885</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44801</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44689</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44605</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44521</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44437</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44325</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44241</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44157</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44073</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43961</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43877</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43793</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43709</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43597</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43513</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43429</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43345</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43233</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43149</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43065</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42981</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42862</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42778</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42694</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1788000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1798000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2354000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1681000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1743000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1589000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2160000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1302000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1466000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1364000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1868000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1353000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1299000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1324000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1670000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1220000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>951000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1166000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1389000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>838000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>931000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>844000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1097000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>906000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>889000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>767000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1043000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>750000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>701000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>640000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>919000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>700000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>515000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>545000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7598,112 +7994,120 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>514000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>501000</v>
+      </c>
+      <c r="F83" s="3">
         <v>688000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>472000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>470000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>447000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>601000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>431000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>436000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>447000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>594000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>438000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>436000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>432000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>559000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>402000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>416000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>404000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>505000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>382000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>389000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>369000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>473000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>336000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>352000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>331000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>431000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>327000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>344000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>335000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>441000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>320000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>312000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>297000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7806,8 +8210,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7910,8 +8320,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8014,8 +8430,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8118,8 +8540,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8222,112 +8650,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2748000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3260000</v>
+      </c>
+      <c r="F89" s="3">
         <v>2958000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2999000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>731000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>4651000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>3725000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1541000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3192000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2610000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2506000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1227000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>401000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3258000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2940000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>3333000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>38000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2647000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>4242000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1898000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>619000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2102000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2293000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2105000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-219000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>2177000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1554000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2105000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>109000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2006000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1834000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>1606000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>493000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>2793000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-169000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8364,112 +8804,120 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1137000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1264000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1577000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1031000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1040000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1556000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-820000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-890000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1057000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1259000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-854000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-723000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1055000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1094000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1028000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-573000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-893000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-852000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-698000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-545000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-715000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-672000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-587000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-730000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-1056000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-585000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-508000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-820000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-779000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-540000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-516000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-667000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-849000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8572,8 +9020,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8676,112 +9130,124 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1022000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-985000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1703000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-954000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-366000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-808000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1057000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1487000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-481000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-912000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1155000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1343000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-355000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-682000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-941000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1850000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-470000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-630000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-920000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-774000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-434000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1095000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-785000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-816000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-498000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-397000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-655000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-1025000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8818,112 +9284,120 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>514000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>515000</v>
       </c>
       <c r="F96" s="3">
-        <v>452000</v>
+        <v>514000</v>
       </c>
       <c r="G96" s="3">
-        <v>905000</v>
+        <v>515000</v>
       </c>
       <c r="H96" s="3">
         <v>452000</v>
       </c>
       <c r="I96" s="3">
+        <v>905000</v>
+      </c>
+      <c r="J96" s="3">
+        <v>452000</v>
+      </c>
+      <c r="K96" s="3">
         <v>399000</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-400000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-797000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-351000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-350000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-698000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-310000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-4430000</v>
       </c>
       <c r="S96" s="3">
         <v>-310000</v>
       </c>
       <c r="T96" s="3">
+        <v>-4430000</v>
+      </c>
+      <c r="U96" s="3">
+        <v>-310000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-619000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-287000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-573000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-286000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-251000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-501000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-250000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-219000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-220000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-3508000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-198000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>0</v>
       </c>
       <c r="AI96" s="3">
         <v>-198000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>-198000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-394000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9026,8 +9500,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9130,8 +9610,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9234,316 +9720,340 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-241000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1193000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1816000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-698000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-7276000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-974000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-664000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-735000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-352000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-863000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1940000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-676000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-828000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-839000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-719000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-419000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-4650000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-700000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1918000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>2999000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1392000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-836000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-397000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-49000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-700000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-267000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-690000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-165000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-660000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-331000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
         <v>-29000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>82000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-37000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-69000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-142000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-24000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-37000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-69000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-142000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-24000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-14000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>18000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>14000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>48000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>68000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>4000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>46000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>67000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>8000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-52000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1449000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1001000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-498000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1309000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-7916000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3311000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1207000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-477000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2114000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>653000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-990000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-626000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-932000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1493000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1032000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1589000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-4953000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1313000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1451000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>3040000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1241000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>643000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1371000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>933000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-698000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>723000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>178000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1096000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-908000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1143000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>8000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-206000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>1426000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-1505000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>COST</t>
   </si>
@@ -656,491 +656,504 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45788</v>
+      </c>
+      <c r="E7" s="2">
         <v>45704</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45620</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45536</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45424</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45340</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45256</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45172</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45053</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44969</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44885</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44801</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44689</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44605</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44521</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44437</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44325</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44241</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44157</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44073</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43961</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43877</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43793</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43709</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43597</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43513</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43429</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43345</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43233</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43149</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43065</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42981</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42862</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42778</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42694</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>63205000</v>
+      </c>
+      <c r="E8" s="3">
         <v>63723000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>62151000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>79697000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>58515000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>58442000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>57799000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>78939000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>53648000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>55266000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>54437000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>72091000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>52596000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>51904000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>50363000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>62675000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>45277000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>44769000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>43208000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>53383000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>37266000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>39072000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>37040000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>47498000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>34740000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>35396000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>35069000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>44411000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>32361000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>32995000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>31809000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>42300000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>28860000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>29766000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>28099000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>36560000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>54996000</v>
+      </c>
+      <c r="E9" s="3">
         <v>55744000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>54109000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>69588000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>51173000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>51140000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>50457000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>69219000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>46877000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>48423000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>47769000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>63558000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>46355000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>45517000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>43952000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>54733000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>39415000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>39078000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>37458000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>46337000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>32205000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>34056000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>32233000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>41310000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>30233000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>30720000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>30623000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>38671000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>28131000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>28733000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>27617000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>36697000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>24970000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>25927000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>24288000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>31649000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8209000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7979000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8042000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10109000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7342000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7302000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7342000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9720000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6771000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6843000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6668000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8533000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6241000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6387000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6411000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7942000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5862000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5691000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5750000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7046000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5061000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5016000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4807000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6188000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4507000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4676000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4446000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5740000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4230000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4262000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4192000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5603000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3890000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3839000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3811000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4911000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1179,8 +1192,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1289,8 +1303,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1399,8 +1416,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1422,20 +1442,20 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>298000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1444,28 +1464,28 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>118000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>84000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>57000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>246000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>212000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>370000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>302000</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1482,8 +1502,8 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1509,8 +1529,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1518,37 +1541,37 @@
         <v>552000</v>
       </c>
       <c r="E15" s="3">
+        <v>552000</v>
+      </c>
+      <c r="F15" s="3">
         <v>548000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>706000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>516000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>514000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>501000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>688000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>472000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>470000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>8</v>
@@ -1568,20 +1591,20 @@
       <c r="U15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W15" s="3">
         <v>16000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>7000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>4000</v>
       </c>
       <c r="Y15" s="3">
         <v>4000</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
+      <c r="Z15" s="3">
+        <v>4000</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>8</v>
@@ -1598,8 +1621,8 @@
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1619,8 +1642,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1656,228 +1682,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>60675000</v>
+      </c>
+      <c r="E17" s="3">
         <v>61407000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>59955000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>76655000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>56318000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>56380000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>55815000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>76158000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>51671000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>53363000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52686000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>69594000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50805000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>50092000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>48670000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>60400000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43614000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>43429000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>41778000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>51454000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>36087000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>37806000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>35979000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>46035000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>33618000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>34193000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>34120000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>42965000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>31294000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>31979000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>30858000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>40850000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>27892000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>28922000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>27250000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>35369000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2530000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2316000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2196000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3042000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2197000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2062000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1984000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2781000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1977000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1903000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1751000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2497000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1791000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1812000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1693000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2275000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1663000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1340000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1430000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1929000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1179000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1266000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1061000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1463000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1122000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1203000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>949000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1446000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1067000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1016000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>951000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1450000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>968000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>844000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>849000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1191000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1916,314 +1949,321 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-33000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-51000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>18000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-34000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-69000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-37000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-18000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>53000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>67000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>71000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>25000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>42000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>68000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>27000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>19000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>29000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-9000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>21000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>45000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>35000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>74000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>36000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>46000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>22000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>51000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>41000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>7000</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>22000</v>
       </c>
       <c r="AH20" s="3">
         <v>22000</v>
       </c>
       <c r="AI20" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>26000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3072000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2901000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2795000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3730000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2747000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2645000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2491000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3506000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2467000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2382000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2251000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3158000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2300000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2273000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2167000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2902000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2092000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1775000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1863000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2425000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1582000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1700000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1465000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2010000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1494000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1601000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1302000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1928000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1435000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1367000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1308000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1913000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1152000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1172000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1628000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E22" s="3">
         <v>36000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>37000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>49000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>41000</v>
       </c>
       <c r="H22" s="3">
         <v>41000</v>
       </c>
       <c r="I22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="J22" s="3">
         <v>38000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>56000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>36000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>34000</v>
       </c>
       <c r="M22" s="3">
         <v>34000</v>
       </c>
       <c r="N22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="O22" s="3">
         <v>48000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>35000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>36000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>39000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>52000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>40000</v>
       </c>
       <c r="T22" s="3">
         <v>40000</v>
       </c>
       <c r="U22" s="3">
+        <v>40000</v>
+      </c>
+      <c r="V22" s="3">
         <v>39000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>51000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>37000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>34000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>38000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>45000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>35000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>34000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>36000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>48000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>37000</v>
       </c>
       <c r="AF22" s="3">
         <v>37000</v>
@@ -2232,242 +2272,251 @@
         <v>37000</v>
       </c>
       <c r="AH22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>53000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>31000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>29000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2580000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2422000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2306000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3113000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2284000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2237000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2106000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2963000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1771000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1983000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1770000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2516000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1827000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1801000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1696000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2291000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1650000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1319000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1420000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1869000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1163000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1277000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1058000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1123000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1215000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>935000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1449000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1071000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>986000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>936000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1419000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>965000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>809000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>846000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1181000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>677000</v>
+      </c>
+      <c r="E24" s="3">
         <v>634000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>508000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>759000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>603000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>494000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>517000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>803000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>469000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>517000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>406000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>638000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>455000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>481000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>351000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>597000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>417000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>348000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>239000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>465000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>311000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>330000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>202000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>340000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>280000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>377000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>185000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>402000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>310000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>247000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>285000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>487000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>259000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>288000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>291000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>396000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2576,228 +2625,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1903000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1788000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1798000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2354000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1681000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1743000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1589000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2160000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1302000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1466000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1364000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1878000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1372000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1320000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1345000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1694000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1233000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>971000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1181000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1404000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>852000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>947000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>856000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1152000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>843000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>838000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>750000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>761000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>739000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>651000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>932000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>706000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>521000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>555000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>785000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1903000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1788000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1798000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2354000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1681000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1743000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1589000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2160000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1302000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1466000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1364000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1868000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1353000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1299000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1324000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1670000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1220000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>951000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1166000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1389000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>838000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>931000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>844000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1139000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>833000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>826000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>740000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1037000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>749000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>727000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>640000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>919000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>700000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>515000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>545000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2906,8 +2964,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2956,8 +3017,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2965,11 +3026,11 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2977,29 +3038,29 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-42000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>73000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>63000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>27000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>6000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>1000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-26000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3016,8 +3077,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3126,8 +3190,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3236,228 +3303,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>33000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>51000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-18000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>34000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>69000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>37000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>18000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-53000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-67000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-71000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-42000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-68000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-27000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-19000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-29000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>9000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-21000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-45000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-74000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-7000</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-22000</v>
       </c>
       <c r="AH32" s="3">
         <v>-22000</v>
       </c>
       <c r="AI32" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>4000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1903000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1788000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1798000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2354000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1681000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1743000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1589000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2160000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1302000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1466000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1364000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1868000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1353000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1299000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1324000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1670000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1220000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>951000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1166000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1389000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>838000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>931000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>844000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1097000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>906000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>889000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>767000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1043000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>750000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>701000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>640000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>919000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>700000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>515000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>545000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3566,233 +3642,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1903000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1788000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1798000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2354000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1681000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1743000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1589000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2160000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1302000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1466000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1364000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1868000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1353000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1299000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1324000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1670000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1220000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>951000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1166000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1389000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>838000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>931000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>844000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1097000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>906000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>889000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>767000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1043000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>750000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>701000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>640000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>919000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>700000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>515000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>545000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45788</v>
+      </c>
+      <c r="E38" s="2">
         <v>45704</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45620</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45536</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45424</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45340</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45256</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45172</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45053</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44969</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44885</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44801</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44689</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44605</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44521</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44437</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44325</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44241</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44157</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44073</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43961</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43877</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43793</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43709</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43597</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43513</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43429</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43345</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43233</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43149</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43065</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42981</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42862</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42778</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42694</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3831,8 +3916,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3871,668 +3957,687 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13836000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12356000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10907000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9906000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10404000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9095000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17011000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13700000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12493000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12970000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10856000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10203000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11193000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11819000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12751000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11258000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10226000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8637000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13590000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12277000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10826000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7786000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9027000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8384000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7013000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6080000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6778000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6055000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5877000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4781000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5689000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4546000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4538000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4744000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4805000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3379000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1014000</v>
+      </c>
+      <c r="E42" s="3">
         <v>802000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>920000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1238000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1095000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1226000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>853000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1534000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1215000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>735000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>817000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>846000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>638000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>477000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>725000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>917000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>900000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>617000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>833000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1028000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>948000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>929000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>993000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1060000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1154000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1042000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1175000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1204000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1167000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1049000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1196000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1233000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1187000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1221000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1311000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1350000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2875000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3060000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2963000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2721000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2583000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2779000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2542000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2285000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2502000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2714000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2312000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2241000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1991000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2232000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1932000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1803000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1595000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1934000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1646000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1550000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1507000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1988000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1711000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1535000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1704000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1995000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1795000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1669000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1593000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2001000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1559000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1432000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1462000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1597000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1498000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1252000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18606000</v>
+      </c>
+      <c r="E44" s="3">
         <v>18754000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20979000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18647000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17430000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>17075000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18001000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16651000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16324000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>16081000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>18571000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>17907000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>17623000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>16485000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>16942000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>14215000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13975000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13865000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>14901000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>12242000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>11010000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>11850000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13818000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>11395000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>11304000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>11356000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>12205000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>11040000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>10626000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>10671000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>11213000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>9834000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>9736000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>9530000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>10721000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>8969000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1820000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1925000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1754000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1734000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1776000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1971000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1673000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1709000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1755000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1830000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1594000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1499000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1563000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1552000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1500000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1312000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1220000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1255000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1126000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1023000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>963000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1150000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1094000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1111000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1110000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1175000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1001000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>321000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>430000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>397000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>240000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>272000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>333000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>368000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>235000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>268000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38151000</v>
+      </c>
+      <c r="E46" s="3">
         <v>36897000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37523000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>34246000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33288000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>32146000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40080000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35879000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>34289000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>34330000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>34150000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>32696000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>33008000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32565000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>33850000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29505000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>27916000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>26308000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>32096000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>28120000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>25254000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>23703000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>26643000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>23485000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>22285000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>21648000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>22954000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>20289000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19693000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>18899000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>19897000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17317000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17256000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>17460000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>18570000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>15218000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4563,8 +4668,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4641,118 +4746,124 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33300000</v>
+      </c>
+      <c r="E48" s="3">
         <v>32340000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31875000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33082000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30705000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30341000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29840000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30722000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28737000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28583000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27931000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27420000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26874000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26892000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26790000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26382000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26052000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>25418000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>25073000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>25187000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24276000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24077000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>23834000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20890000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20475000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20145000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19879000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19681000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19178000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19049000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18682000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>18161000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>17535000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>17342000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>17156000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>17043000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4763,11 +4874,11 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>994000</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -4775,16 +4886,16 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>994000</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>8</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>8</v>
@@ -4798,26 +4909,26 @@
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3">
+      <c r="R49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S49" s="3">
         <v>1290000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1234000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1235000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1217000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1271000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1242000</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>8</v>
@@ -4834,8 +4945,8 @@
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE49" s="3">
         <v>0</v>
@@ -4861,8 +4972,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4971,8 +5085,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5081,118 +5198,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4031000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3987000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3988000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>961000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3918000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3836000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3803000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>908000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3726000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3935000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3946000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4050000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3970000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3621000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3509000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2091000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2072000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1957000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1831000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>978000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>960000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1002000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>954000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1025000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>992000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1006000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>981000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>860000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>734000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>755000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>799000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>869000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>840000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>828000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>806000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>902000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5301,118 +5424,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>75482000</v>
+      </c>
+      <c r="E54" s="3">
         <v>73224000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73386000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>69831000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>67911000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66323000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>73723000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>68994000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>66752000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66848000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>66027000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>64166000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>63852000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>63078000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>64149000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>59268000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>57274000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>54918000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>60217000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>55556000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>51732000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>48782000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>51431000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>45400000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>43752000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>42799000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>43814000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>40830000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>39605000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>38703000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>39378000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>36347000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>35631000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>35630000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>36532000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>33163000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5451,8 +5580,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5491,668 +5621,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19820000</v>
+      </c>
+      <c r="E57" s="3">
         <v>18610000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21793000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19421000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18844000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17494000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20357000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17483000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16853000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16407000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18348000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17848000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17651000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17089000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19561000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16278000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15538000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14383000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17014000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14172000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10813000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11072000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14440000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11679000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11331000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10711000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13133000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11237000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10705000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10061000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11992000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9608000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9425000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>8764000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>11003000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>7612000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>178000</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>97000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>429000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1077000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1080000</v>
       </c>
       <c r="I58" s="3">
         <v>1080000</v>
       </c>
       <c r="J58" s="3">
+        <v>1080000</v>
+      </c>
+      <c r="K58" s="3">
         <v>1430000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>76000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>71000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>73000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>77000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
-        <v>799000</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>799000</v>
       </c>
       <c r="S58" s="3">
+        <v>799000</v>
+      </c>
+      <c r="T58" s="3">
         <v>92000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>95000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>96000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>126000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1526000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>518000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1712000</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>1699000</v>
       </c>
       <c r="AA58" s="3">
         <v>1699000</v>
       </c>
       <c r="AB58" s="3">
+        <v>1699000</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1698000</v>
       </c>
-      <c r="AC58" s="3" t="s">
+      <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>90000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>119000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>122000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>116000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>86000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1158000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2257000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1159000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1100000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10185000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10748000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9170000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8385000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8736000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9045000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8650000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8242000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8662000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9534000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14648000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14077000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14117000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14456000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12982000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12364000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12352000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12086000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15557000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10546000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10440000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11105000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10113000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9859000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9802000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10041000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8599000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8587000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8730000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8252000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7801000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>10811000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7839000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6999000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>6863000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>37579000</v>
+      </c>
+      <c r="E60" s="3">
         <v>36999000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38289000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35464000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35361000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34688000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36768000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33583000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31708000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32516000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33067000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31998000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31845000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31545000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>33342000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>29441000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27982000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26564000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>32667000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24844000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>22779000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>22695000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>26265000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>23237000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>22832000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>22450000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>22473000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19926000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>19411000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18913000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>20360000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>17495000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>21394000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>18860000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>19161000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>15575000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8180000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8039000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8033000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9520000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8220000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8353000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8267000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9106000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9004000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9063000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6472000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6484000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6507000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6658000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6667000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6692000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7495000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7522000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7529000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8171000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8227000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5643000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5495000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5124000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4799000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4794000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6480000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6487000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6492000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6505000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6478000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6573000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2821000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2815000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3933000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4061000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2598000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2609000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2613000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>456000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2559000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2522000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2541000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>452000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2467000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2470000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5012000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5037000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4987000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4899000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5140000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5057000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4823000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4703000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4712000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3836000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3523000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3445000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3447000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1455000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1301000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1372000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1382000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1314000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1255000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1232000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1184000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1200000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1231000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1243000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1207000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1195000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6261,8 +6410,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6371,8 +6523,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6481,118 +6636,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48357000</v>
+      </c>
+      <c r="E66" s="3">
         <v>47647000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48935000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>46209000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46140000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45563000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47576000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43936000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43179000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>44049000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>44556000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>43524000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43884000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43660000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45686000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>41704000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>40792000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>39266000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>45357000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>37272000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34930000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>32168000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>35570000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>30157000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>29266000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>28941000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>30647000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>28031000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>27462000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>26949000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>28300000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>25569000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>25733000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23190000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>24559000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>21084000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6631,8 +6792,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6741,8 +6903,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6851,8 +7016,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6961,8 +7129,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7071,118 +7242,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20890000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19770000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18700000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17619000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15989000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14980000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20499000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19521000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18035000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17341000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16412000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15585000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14294000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13474000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12606000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11666000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10466000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9766000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9232000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12879000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11883000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11384000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10787000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10258000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9496000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8916000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8387000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>7887000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>7176000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6727000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6300000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5988000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5508000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8140000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>7882000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>7686000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7291,8 +7468,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7401,8 +7581,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7511,118 +7694,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27125000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25577000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24451000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23622000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21771000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20760000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26147000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25058000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23568000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22794000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21471000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20642000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19968000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19418000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18463000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17564000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16482000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15652000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14860000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18284000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16802000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16614000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15861000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15243000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14486000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13858000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13167000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12799000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12143000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11754000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11078000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10778000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9898000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12440000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>11973000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12079000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7731,233 +7920,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45788</v>
+      </c>
+      <c r="E80" s="2">
         <v>45704</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45620</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45536</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45424</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45340</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45256</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45172</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45053</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44969</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44885</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44801</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44689</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44605</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44521</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44437</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44325</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44241</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44157</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44073</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43961</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43877</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43793</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43709</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43597</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43513</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43429</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43345</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43233</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43149</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43065</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42981</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42862</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42778</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42694</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1903000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1788000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1798000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2354000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1681000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1743000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1589000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2160000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1302000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1466000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1364000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1868000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1353000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1299000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1324000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1670000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1220000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>951000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1166000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1389000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>838000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>931000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>844000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1097000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>906000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>889000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>767000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1043000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>750000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>701000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>640000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>919000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>700000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>515000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>545000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7996,118 +8194,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>516000</v>
+      </c>
+      <c r="E83" s="3">
         <v>514000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>501000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>688000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>472000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>470000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>447000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>601000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>431000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>436000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>447000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>594000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>438000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>436000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>432000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>559000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>402000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>416000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>404000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>505000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>382000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>389000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>369000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>473000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>336000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>352000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>331000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>431000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>327000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>344000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>335000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>441000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>320000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>312000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>297000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8216,8 +8418,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8326,8 +8531,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8436,8 +8644,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8546,8 +8757,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8656,118 +8870,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3460000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2748000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3260000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2958000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2999000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>731000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4651000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3725000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1541000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3192000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2610000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2506000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1227000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>401000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3258000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2940000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3333000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>38000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2647000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4242000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1898000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>619000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2102000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2293000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2105000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-219000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2177000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1554000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2105000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>109000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2006000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1834000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1606000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>493000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2793000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-169000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8806,118 +9026,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1131000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1264000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1577000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1031000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1040000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1556000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-820000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-890000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1057000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1259000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-854000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-723000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1055000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1094000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1028000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-573000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-893000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-852000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-698000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-545000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-715000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-672000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-587000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-730000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1056000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-585000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-508000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-820000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-779000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-540000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-516000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-667000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-849000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9026,8 +9250,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9136,118 +9363,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1336000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1022000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-985000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1703000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-954000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-366000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-808000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1057000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1487000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-481000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-912000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1155000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1343000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-355000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-682000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-941000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1850000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-470000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-630000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-920000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-774000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-434000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1095000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-785000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-816000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-498000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-397000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-655000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1025000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9286,118 +9519,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>515000</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>515000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>514000</v>
       </c>
-      <c r="G96" s="3">
-        <v>515000</v>
-      </c>
       <c r="H96" s="3">
+        <v>7170000</v>
+      </c>
+      <c r="I96" s="3">
         <v>452000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>905000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>452000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>399000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-400000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-797000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-351000</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-350000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-698000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-310000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-4430000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-310000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-619000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-287000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-573000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-286000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-251000</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-501000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-250000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-219000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-220000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-3508000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-198000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-198000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-394000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9506,8 +9743,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9616,8 +9856,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9726,334 +9969,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-748000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-241000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1193000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1816000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-698000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7276000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-974000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-664000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-735000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-352000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-863000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1940000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-676000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-828000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-839000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-719000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-419000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4650000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-700000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1918000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2999000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1392000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-836000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-49000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-700000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-267000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-690000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-165000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-660000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-331000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E101" s="3">
         <v>15000</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-29000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>82000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-37000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-69000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-142000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-24000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-37000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-69000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-142000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-14000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-34000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>18000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>14000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>48000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>68000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA101" s="3">
         <v>-1000</v>
       </c>
       <c r="AB101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC101" s="3">
         <v>4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>46000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>67000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>8000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-52000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1480000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1449000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1001000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-498000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1309000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7916000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3311000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1207000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-477000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2114000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>653000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-990000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-626000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-932000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1493000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1032000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1589000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4953000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1313000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1451000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3040000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1241000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>643000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1371000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>933000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-698000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>723000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>178000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1096000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-908000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1143000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>8000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-206000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1426000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1505000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>COST</t>
   </si>
@@ -656,517 +656,542 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46068</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45984</v>
+      </c>
+      <c r="F7" s="2">
         <v>45900</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45788</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45704</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45620</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45536</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45424</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45340</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45256</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45172</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45053</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44969</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44885</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44801</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44689</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44605</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44521</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44437</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44325</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44241</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44157</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44073</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43961</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43877</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43793</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43709</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43597</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43513</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43429</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43345</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43233</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43149</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43065</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42981</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42862</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42778</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42694</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>69597000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>67307000</v>
+      </c>
+      <c r="F8" s="3">
         <v>86156000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>63205000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>63723000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>62151000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>79697000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>58515000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>58442000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>57799000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>78939000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>53648000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>55266000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>54437000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>72091000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>52596000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>51904000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>50363000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>62675000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>45277000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>44769000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>43208000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>53383000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>37266000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>39072000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>37040000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>47498000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>34740000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>35396000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>35069000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>44411000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>32361000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>32995000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>31809000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>42300000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>28860000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>29766000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>28099000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>36560000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>60719000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>58510000</v>
+      </c>
+      <c r="F9" s="3">
         <v>75037000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>54996000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>55744000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>54109000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>69588000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>51173000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>51140000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>50457000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>69219000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>46877000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>48423000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>47769000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>63558000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>46355000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>45517000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>43952000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>54733000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>39415000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>39078000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>37458000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>46337000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>32205000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>34056000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>32233000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>41310000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>30233000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>30720000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>30623000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>38671000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>28131000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>28733000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>27617000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>36697000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>24970000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>25927000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>24288000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>31649000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8878000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>8797000</v>
+      </c>
+      <c r="F10" s="3">
         <v>11119000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>8209000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>7979000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>8042000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>10109000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>7342000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>7302000</v>
       </c>
       <c r="K10" s="3">
         <v>7342000</v>
       </c>
       <c r="L10" s="3">
+        <v>7302000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>7342000</v>
+      </c>
+      <c r="N10" s="3">
         <v>9720000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>6771000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>6843000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6668000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>8533000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>6241000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>6387000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>6411000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>7942000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>5862000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>5691000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>5750000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>7046000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>5061000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>5016000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>4807000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>6188000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>4507000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>4676000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>4446000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>5740000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>4230000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>4262000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>4192000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>5603000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>3890000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>3839000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>3811000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>4911000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1232,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1323,8 +1350,14 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1439,8 +1472,14 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1468,53 +1507,53 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>298000</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>118000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>84000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>57000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>246000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>212000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>370000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>302000</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1528,11 +1567,11 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1555,55 +1594,61 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>597000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>597000</v>
+      </c>
+      <c r="F15" s="3">
         <v>774000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>552000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>552000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>548000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>706000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>516000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>514000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>501000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>688000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>472000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>470000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>8</v>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
@@ -1620,23 +1665,23 @@
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z15" s="3">
         <v>16000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>7000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>4000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>4000</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
@@ -1650,11 +1695,11 @@
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>0</v>
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ15" s="3">
         <v>0</v>
@@ -1671,8 +1716,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,240 +1761,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>66991000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>64844000</v>
+      </c>
+      <c r="F17" s="3">
         <v>82815000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>60675000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>61407000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>59955000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>76655000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>56318000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>56380000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>55815000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>76158000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>51671000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>53363000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>52686000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>69594000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>50805000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>50092000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>48670000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>60400000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>43614000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>43429000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>41778000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>51454000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>36087000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>37806000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>35979000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>46035000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>33618000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>34193000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>34120000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>42965000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>31294000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>31979000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>30858000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>40850000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>27892000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>28922000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>27250000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>35369000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2606000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2463000</v>
+      </c>
+      <c r="F18" s="3">
         <v>3341000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2530000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2316000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>2196000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3042000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>2197000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2062000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1984000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2781000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1977000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1903000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1751000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2497000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1791000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1812000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1693000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2275000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1663000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1340000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1430000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1929000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1179000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1266000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1061000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1463000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1122000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1203000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>949000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1446000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1067000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>1016000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>951000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>1450000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>968000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>844000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>849000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>1191000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1984,588 +2049,620 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-46000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-33000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-51000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>18000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-34000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-69000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-37000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-18000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>53000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>67000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>71000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>25000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>42000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>68000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>27000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>19000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>29000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>21000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>45000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>35000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>74000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>36000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>46000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>22000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>51000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>41000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>7000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>22000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>18000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>26000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3211000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3093000</v>
+      </c>
+      <c r="F21" s="3">
         <v>4161000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>3072000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2901000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2795000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3730000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2747000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2645000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2491000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3506000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2467000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2382000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2251000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3158000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2300000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2273000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2167000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2902000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2092000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1775000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1863000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2425000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1582000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1465000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>2010000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1494000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1601000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1302000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>1928000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>1435000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>1367000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1308000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>1913000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>1152000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>1172000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>1628000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>46000</v>
+        <v>33000</v>
       </c>
       <c r="E22" s="3">
         <v>35000</v>
       </c>
       <c r="F22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="H22" s="3">
         <v>36000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>37000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>49000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>41000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>41000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>38000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>56000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>36000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>34000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>34000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>48000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>35000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>36000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>39000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>52000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>40000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>40000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>39000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>51000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>37000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>34000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>38000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>45000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>35000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>34000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>36000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>48000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>37000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>37000</v>
       </c>
       <c r="AI22" s="3">
         <v>37000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AL22" s="3">
         <v>53000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>21000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>31000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>29000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2721000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2583000</v>
+      </c>
+      <c r="F23" s="3">
         <v>3510000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2580000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2422000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2306000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3113000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2284000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2237000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2106000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2963000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1771000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1983000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1770000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2516000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1827000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1801000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1696000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2291000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1650000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1319000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1420000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1869000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1163000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1277000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1058000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1492000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1123000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>1215000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>935000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>1449000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>1071000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>986000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>936000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>1419000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>965000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>809000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>846000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>1181000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>686000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>582000</v>
+      </c>
+      <c r="F24" s="3">
         <v>900000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>677000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>634000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>508000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>759000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>603000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>494000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>517000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>803000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>469000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>517000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>406000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>638000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>455000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>481000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>351000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>597000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>417000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>348000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>239000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>465000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>311000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>330000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>202000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>340000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>280000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>377000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>185000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>402000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>310000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>247000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>285000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>487000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>259000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>288000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>291000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>396000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2680,240 +2777,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2035000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2001000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2610000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1903000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1788000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1798000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2354000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1681000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1743000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1589000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2160000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1302000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1466000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1364000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1878000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1372000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1320000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1345000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1694000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1233000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>971000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1181000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1404000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>852000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>947000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>856000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1152000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>843000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>838000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>750000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>1047000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>761000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>739000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>651000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>932000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>706000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>521000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>555000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>785000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2035000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2001000</v>
+      </c>
+      <c r="F27" s="3">
         <v>2610000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1903000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1788000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1798000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2354000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1681000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1743000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1589000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2160000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1302000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1466000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1364000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1868000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1353000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1299000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1324000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1670000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1220000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>951000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1166000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1389000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>838000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>931000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>844000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1139000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>833000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>826000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>740000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>1037000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>749000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>727000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>640000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>919000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>700000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>515000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>545000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3028,8 +3143,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3084,53 +3205,53 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-42000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>73000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>63000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>27000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>6000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AI29" s="3">
         <v>1000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AJ29" s="3">
         <v>-26000</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3144,8 +3265,14 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3260,8 +3387,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3376,240 +3509,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F32" s="3">
         <v>46000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>33000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>51000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-18000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>34000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>69000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>37000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>18000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-53000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-71000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-25000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-42000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-68000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-27000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-19000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-29000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>9000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-45000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-74000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>4000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2035000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2001000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2610000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1903000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1788000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1798000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2354000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1681000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1743000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1589000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2160000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1302000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1466000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1364000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1868000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1353000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1299000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1324000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1670000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1220000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>951000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1166000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1389000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>838000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>931000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>844000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1097000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>906000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>889000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>767000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>1043000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>750000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>701000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>640000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>919000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>700000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>515000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>545000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3724,245 +3875,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2035000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2001000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2610000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1903000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1788000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1798000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2354000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1681000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1743000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1589000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2160000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1302000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1466000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1364000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1868000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1353000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1299000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1324000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1670000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1220000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>951000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1166000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1389000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>838000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>931000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>844000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1097000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>906000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>889000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>767000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>1043000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>750000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>701000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>640000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>919000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>700000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>515000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>545000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46068</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45984</v>
+      </c>
+      <c r="F38" s="2">
         <v>45900</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45788</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45704</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45620</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45536</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45424</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45340</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45256</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45172</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45053</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44969</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44885</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44801</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44689</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44605</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44521</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44437</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44325</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44241</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44157</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44073</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43961</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43877</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43793</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43709</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43597</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43513</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43429</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43345</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43233</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43149</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43065</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42981</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42862</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42778</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42694</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4003,8 +4172,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4045,704 +4216,742 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17383000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16217000</v>
+      </c>
+      <c r="F41" s="3">
         <v>14161000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>13836000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12356000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>10907000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9906000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10404000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9095000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>17011000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>13700000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>12493000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12970000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10856000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>10203000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>11193000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>11819000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>12751000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>11258000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>10226000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>8637000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>13590000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>12277000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>10826000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>7786000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>9027000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>8384000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>7013000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>6080000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>6778000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>6055000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>5877000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>4781000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>5689000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>4546000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>4538000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>4744000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>4805000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>3379000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>857000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>966000</v>
+      </c>
+      <c r="F42" s="3">
         <v>1123000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1014000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>802000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>920000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1238000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1095000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1226000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>853000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1534000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1215000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>735000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>817000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>846000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>638000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>477000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>725000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>917000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>900000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>617000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>833000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1028000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>948000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>929000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>993000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1060000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1154000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1042000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1175000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>1204000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>1167000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>1049000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>1196000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>1233000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>1187000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>1221000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>1311000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>1350000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3782000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3231000</v>
+      </c>
+      <c r="F43" s="3">
         <v>3203000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2875000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3060000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2963000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2721000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2583000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2779000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2542000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2285000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2502000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2714000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2312000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2241000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1991000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2232000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1932000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1803000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1595000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1934000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1646000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1550000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1507000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1988000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1711000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1535000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1704000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1995000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>1795000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1669000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>1593000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>2001000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>1559000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>1432000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>1462000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>1597000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>1498000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>1252000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18991000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>21141000</v>
+      </c>
+      <c r="F44" s="3">
         <v>18116000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>18606000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>18754000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>20979000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>18647000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>17430000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>17075000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>18001000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>16651000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>16324000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>16081000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>18571000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>17907000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>17623000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>16485000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>16942000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>14215000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>13975000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>13865000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>14901000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>12242000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>11010000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>11850000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>13818000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>11395000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>11304000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>11356000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>12205000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>11040000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>10626000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>10671000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>11213000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>9834000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>9736000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>9530000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>10721000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>8969000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2120000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1856000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1777000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1820000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1925000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1754000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1734000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1776000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1971000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1673000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1709000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1755000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1830000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1594000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1499000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1563000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1552000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1500000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1312000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1220000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1255000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1126000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1023000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>963000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1150000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1094000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1111000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1110000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1175000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1001000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>321000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>430000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>397000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>240000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>272000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>333000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>368000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>235000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>268000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>43133000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>43411000</v>
+      </c>
+      <c r="F46" s="3">
         <v>38380000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>38151000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>36897000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>37523000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>34246000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>33288000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>32146000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>40080000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>35879000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>34289000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>34330000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>34150000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>32696000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>33008000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>32565000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>33850000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>29505000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>27916000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>26308000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>32096000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>28120000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>25254000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>23703000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>26643000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>23485000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>22285000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>21648000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>22954000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>20289000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>19693000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>18899000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>19897000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>17317000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>17256000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>17460000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>18570000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>15218000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4779,11 +4988,11 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4857,165 +5066,177 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36404000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>35346000</v>
+      </c>
+      <c r="F48" s="3">
         <v>36122000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>33300000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>32340000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>31875000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>33082000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>30705000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>30341000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>29840000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>30722000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>28737000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>28583000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>27931000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>27420000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>26874000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>26892000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>26790000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>26382000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>26052000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>25418000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>25073000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>25187000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>24276000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>24077000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>23834000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>20890000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>20475000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>20145000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>19879000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>19681000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>19178000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>19049000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>18682000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>18161000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>17535000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>17342000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>17156000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>17043000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>953000</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>26000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>994000</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
@@ -5026,29 +5247,29 @@
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V49" s="3">
         <v>1290000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1234000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1235000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1217000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1271000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1242000</v>
-      </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>8</v>
@@ -5062,11 +5283,11 @@
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>0</v>
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH49" s="3">
         <v>0</v>
@@ -5089,8 +5310,14 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5205,8 +5432,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5321,124 +5554,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4102000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4033000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1052000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>4031000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3987000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3988000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1929000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3918000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3836000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3803000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>908000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3726000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3935000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3946000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4050000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3970000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3621000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3509000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2091000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2072000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1957000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1831000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>978000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>960000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1002000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>954000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1025000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>992000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1006000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>981000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>860000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>734000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>755000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>799000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>869000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>840000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>828000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>806000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>902000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5553,124 +5798,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>83639000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>82790000</v>
+      </c>
+      <c r="F54" s="3">
         <v>77099000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>75482000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>73224000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>73386000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>69831000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>67911000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>66323000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>73723000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>68994000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>66752000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>66848000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>66027000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>64166000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>63852000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>63078000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>64149000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>59268000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>57274000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>54918000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>60217000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>55556000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>51732000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>48782000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>51431000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>45400000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>43752000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>42799000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>43814000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>40830000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>39605000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>38703000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>39378000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>36347000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>35631000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>35630000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>36532000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>33163000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5711,8 +5968,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5753,704 +6012,742 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20647000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>23513000</v>
+      </c>
+      <c r="F57" s="3">
         <v>19783000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>19820000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>18610000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>21793000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>19421000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>18844000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>17494000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>20357000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>17483000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>16853000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>16407000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>18348000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>17848000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>17651000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>17089000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>19561000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>16278000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>15538000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>14383000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>17014000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>14172000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>10813000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>11072000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>14440000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>11679000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>11331000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>10711000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>13133000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>11237000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>10705000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>10061000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>11992000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>9608000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>9425000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>8764000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>11003000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>7612000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>170000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>70000</v>
+      </c>
+      <c r="F58" s="3">
         <v>361000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>178000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>97000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>429000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1077000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1080000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1080000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1430000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>76000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>71000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>73000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>77000</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>799000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>799000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>92000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>95000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>96000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>126000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1526000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>518000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1712000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1699000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1699000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1698000</v>
       </c>
-      <c r="AE58" s="3" t="s">
+      <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>90000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>119000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>122000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>116000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>86000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>1158000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>2257000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>1159000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>1100000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11478000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10338000</v>
+      </c>
+      <c r="F59" s="3">
         <v>9082000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>10185000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>10748000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>9170000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>8385000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>8736000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>9045000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>8650000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>8242000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>8662000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>9534000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>14648000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>14077000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>14117000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>14456000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>12982000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>12364000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>12352000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>12086000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>15557000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>10546000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>10440000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>11105000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>10113000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>9859000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>9802000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>10041000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>9340000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>8599000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>8587000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>8730000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>8252000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>7801000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>10811000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>7839000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>6999000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>6863000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40763000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>41805000</v>
+      </c>
+      <c r="F60" s="3">
         <v>37108000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>37579000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>36999000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>38289000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>35464000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>35361000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>34688000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>36768000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>33583000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>31708000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>32516000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>33067000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>31998000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>31845000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>31545000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>33342000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>29441000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>27982000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>26564000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>32667000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>24844000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>22779000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>22695000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>26265000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>23237000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>22832000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>22450000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>22473000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>19926000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>19411000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>18913000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>20360000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>17495000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>21394000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>18860000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>19161000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>15575000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8165000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8102000</v>
+      </c>
+      <c r="F61" s="3">
         <v>9574000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>8180000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>8039000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>8033000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>9520000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>8220000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8353000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8267000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9106000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>9004000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9063000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6472000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>6484000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>6507000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>6658000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>6667000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>6692000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>7495000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>7522000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>7529000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>8171000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>8227000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>5643000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>5495000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>5124000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>4799000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>4794000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>6480000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>6487000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>6492000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>6505000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>6478000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>6573000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>2821000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>2815000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>3933000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>4061000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2624000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2580000</v>
+      </c>
+      <c r="F62" s="3">
         <v>529000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2598000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2609000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2613000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>456000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2559000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2522000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2541000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>452000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2467000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2470000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>5012000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>5037000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4987000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4899000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>5140000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>5057000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4823000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4703000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>4712000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3836000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3523000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3445000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>3447000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1455000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1301000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1372000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1382000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1314000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1255000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1232000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1184000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1200000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>1231000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>1243000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>1207000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>1195000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6565,8 +6862,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6681,8 +6984,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6797,124 +7106,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>51552000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>52487000</v>
+      </c>
+      <c r="F66" s="3">
         <v>47935000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>48357000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>47647000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>48935000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>46209000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>46140000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>45563000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>47576000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>43936000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>43179000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>44049000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>44556000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>43524000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>43884000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>43660000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>45686000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>41704000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>40792000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>39266000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>45357000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>37272000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>34930000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>32168000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>35570000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>30157000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>29266000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>28941000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>30647000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>28031000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>27462000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>26949000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>28300000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>25569000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>25733000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>23190000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>24559000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>21084000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6955,8 +7276,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7071,8 +7394,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7187,8 +7516,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7303,8 +7638,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7419,124 +7760,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>25121000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>23869000</v>
+      </c>
+      <c r="F72" s="3">
         <v>22650000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>20890000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>19770000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>18700000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>17619000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>15989000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>14980000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>20499000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>19521000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>18035000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>17341000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>16412000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>15585000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>14294000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>13474000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>12606000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>11666000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>10466000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>9766000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>9232000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>12879000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>11883000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>11384000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>10787000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>10258000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>9496000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>8916000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>8387000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>7887000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>7176000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>6727000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>6300000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>5988000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>5508000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>8140000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>7882000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>7686000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7651,8 +8004,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7767,8 +8126,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7883,124 +8248,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32087000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>30303000</v>
+      </c>
+      <c r="F76" s="3">
         <v>29164000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>27125000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>25577000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>24451000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>23622000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>21771000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>20760000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>26147000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>25058000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>23568000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>22794000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>21471000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>20642000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>19968000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>19418000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>18463000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>17564000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>16482000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>15652000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14860000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>18284000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>16802000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>16614000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>15861000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>15243000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>14486000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>13858000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>13167000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>12799000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>12143000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>11754000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>11078000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>10778000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>9898000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>12440000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>11973000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>12079000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8115,245 +8492,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46068</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45984</v>
+      </c>
+      <c r="F80" s="2">
         <v>45900</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45788</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45704</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45620</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45536</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45424</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45340</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45256</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45172</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45053</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44969</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44885</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44801</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44689</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44605</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44521</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44437</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44325</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44241</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44157</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44073</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43961</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43877</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43793</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43709</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43597</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43513</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43429</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43345</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43233</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43149</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43065</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42981</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42862</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42778</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42694</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42610</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2035000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2001000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2610000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1903000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1788000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1798000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2354000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1681000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1743000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1589000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2160000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1302000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1466000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1364000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1868000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1353000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1299000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1324000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1670000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1220000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>951000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1166000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1389000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>838000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>931000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>844000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1097000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>906000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>889000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>767000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>1043000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>750000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>701000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>640000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>919000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>700000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>515000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>545000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>779000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8394,124 +8789,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>548000</v>
+      </c>
+      <c r="F83" s="3">
         <v>706000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>516000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>514000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>501000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>688000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>472000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>470000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>447000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>601000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>431000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>436000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>447000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>594000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>438000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>436000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>432000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>559000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>402000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>416000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>404000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>505000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>382000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>389000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>369000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>473000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>336000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>352000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>331000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>431000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>327000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>344000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>335000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>441000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>320000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>312000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>297000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8626,8 +9029,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8742,8 +9151,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8858,8 +9273,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8974,8 +9395,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9090,124 +9517,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2996000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4688000</v>
+      </c>
+      <c r="F89" s="3">
         <v>3867000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3460000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2748000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>3260000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2958000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2999000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>731000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4651000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3725000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1541000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3192000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2610000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2506000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1227000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>401000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>3258000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2940000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>3333000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>38000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2647000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>4242000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1898000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>619000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>2102000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>2293000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2105000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-219000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2177000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1554000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>2105000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>109000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>2006000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>1834000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>1606000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>493000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>2793000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>-169000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9248,124 +9687,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1289000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1526000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1966000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1131000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1264000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1577000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1031000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1040000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1556000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-820000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-890000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1057000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1259000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-854000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-723000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1055000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1094000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-1028000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-573000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-893000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-852000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-698000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-545000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-715000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-672000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-587000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-730000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-1056000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-585000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-508000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-820000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-779000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-540000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-516000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-667000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-849000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9480,8 +9927,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9596,124 +10049,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1170000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1398000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1968000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1336000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1022000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-985000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1703000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-954000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-366000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-808000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1057000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1487000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-481000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-912000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1155000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1343000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-355000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-682000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-941000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1850000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-470000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-630000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-920000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-774000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-434000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1095000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-373000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-785000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-816000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-498000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-397000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-655000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-1025000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9754,124 +10219,132 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>577000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>577000</v>
+      </c>
+      <c r="F96" s="3">
         <v>1153000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>515000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
       </c>
       <c r="G96" s="3">
         <v>515000</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>515000</v>
+      </c>
+      <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>7170000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>452000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>905000</v>
       </c>
       <c r="L96" s="3">
         <v>452000</v>
       </c>
       <c r="M96" s="3">
+        <v>905000</v>
+      </c>
+      <c r="N96" s="3">
+        <v>452000</v>
+      </c>
+      <c r="O96" s="3">
         <v>399000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-400000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-797000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-351000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-350000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-698000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-310000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-4430000</v>
       </c>
       <c r="W96" s="3">
         <v>-310000</v>
       </c>
       <c r="X96" s="3">
+        <v>-4430000</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>-310000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-619000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-287000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-573000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-286000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-251000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-501000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-250000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-219000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-220000</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-3508000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-198000</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>0</v>
       </c>
       <c r="AM96" s="3">
         <v>-198000</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
+        <v>-198000</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-394000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9986,8 +10459,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10102,8 +10581,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10218,352 +10703,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-730000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1167000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1593000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-748000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-241000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1193000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1816000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-698000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-7276000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-974000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-664000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-735000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-352000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-863000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1940000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-676000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-828000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-839000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-719000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-419000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-4650000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-700000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1918000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>2999000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1392000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-836000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-49000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-700000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-267000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-266000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-690000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-165000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-660000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-331000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="F101" s="3">
         <v>63000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-38000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>15000</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="I101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-29000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>82000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-37000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-69000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-142000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-24000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-37000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-142000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-24000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-14000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-34000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>18000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>14000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>48000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>68000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>4000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-17000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>46000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>67000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>2000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>8000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-52000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1166000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2056000</v>
+      </c>
+      <c r="F102" s="3">
         <v>325000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1480000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1449000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1001000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-498000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1309000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-7916000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>3311000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1207000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-477000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2114000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>653000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-990000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-626000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-932000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1493000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1032000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1589000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-4953000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1313000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1451000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3040000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1241000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>643000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1371000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>933000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-698000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>723000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>178000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>1096000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-908000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>1143000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>8000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-206000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>1426000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>-1505000</v>
       </c>
     </row>
